--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$125</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3051" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4572" uniqueCount="565">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1431,6 +1434,10 @@
     <t>The official certifications, training, and licenses that authorize or otherwise pertain to the provision of care by the practitioner.  For example, a medical license issued by a medical board authorizing the practitioner to practice medicine within a certian locality.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:code}
+</t>
+  </si>
+  <si>
     <t>CER?</t>
   </si>
   <si>
@@ -1496,49 +1503,258 @@
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
+    <t>Specific qualification the practitioner has to provide a service.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v2-2.7-0360</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE</t>
+  </si>
+  <si>
+    <t>./Qualifications.Value</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period</t>
+  </si>
+  <si>
+    <t>Period during which the qualification is valid</t>
+  </si>
+  <si>
+    <t>Period during which the qualification is valid.</t>
+  </si>
+  <si>
+    <t>Qualifications are often for a limited period of time, and can be revoked.</t>
+  </si>
+  <si>
+    <t>DR</t>
+  </si>
+  <si>
+    <t>.playingEntity.playingRole[classCode=QUAL].effectiveTime</t>
+  </si>
+  <si>
+    <t>./Qualifications.StartDate and ./Qualifications.EndDate</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.issuer</t>
+  </si>
+  <si>
+    <t>Organization that regulates and issues the qualification</t>
+  </si>
+  <si>
+    <t>Organization that regulates and issues the qualification.</t>
+  </si>
+  <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>.playingEntity.playingRole[classCode=QUAL].scoper</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree</t>
+  </si>
+  <si>
+    <t>degree</t>
+  </si>
+  <si>
+    <t>Diplôme et type de diplôme, par exemple : DE, DES, CES, etc. (typeDiplome)</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.coding:degreeType</t>
+  </si>
+  <si>
+    <t>degreeType</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J81-TypeDiplome-RASS/FHIR/JDV-J81-TypeDiplome-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.coding:degree</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J105-EnsembleDiplome-RASS/FHIR/JDV-J105-EnsembleDiplome-RASS</t>
   </si>
   <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>./Qualifications.Value</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period</t>
-  </si>
-  <si>
-    <t>Period during which the qualification is valid</t>
-  </si>
-  <si>
-    <t>Period during which the qualification is valid.</t>
-  </si>
-  <si>
-    <t>Qualifications are often for a limited period of time, and can be revoked.</t>
-  </si>
-  <si>
-    <t>DR</t>
-  </si>
-  <si>
-    <t>.playingEntity.playingRole[classCode=QUAL].effectiveTime</t>
-  </si>
-  <si>
-    <t>./Qualifications.StartDate and ./Qualifications.EndDate</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.issuer</t>
-  </si>
-  <si>
-    <t>Organization that regulates and issues the qualification</t>
-  </si>
-  <si>
-    <t>Organization that regulates and issues the qualification.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>.playingEntity.playingRole[classCode=QUAL].scoper</t>
+    <t>Practitioner.qualification:degree.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.issuer</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro</t>
+  </si>
+  <si>
+    <t>exercicePro</t>
+  </si>
+  <si>
+    <t>exercicePro : exercice professionnel décrivant la profession exercée, l'identité d'exercice d'un professionnel et le cadre de son exercice (civil, militaire, etc.).</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:categorieProfession</t>
+  </si>
+  <si>
+    <t>categorieProfession</t>
+  </si>
+  <si>
+    <t>Catégorie professionnelle indiquant si le professionnel exerce sa profession en tant que Militaire, Civil, Fonctionnaire ou Etudiant (categorieProfessionnelle).</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J89-CategorieProfessionnelle-RASS/FHIR/JDV-J89-CategorieProfessionnelle-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:profession</t>
+  </si>
+  <si>
+    <t>profession</t>
+  </si>
+  <si>
+    <t>Profession exercée : de santé (professionSante) TRE G15, du social (professionSocial) TRE R94, à usage de titre professionnel (usagerTitre) TRE R95, ou autre profession (autreProfession) TRE R291</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J106-EnsembleProfession-RASS/FHIR/JDV-J106-EnsembleProfession-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.issuer</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire</t>
+  </si>
+  <si>
+    <t>savoirFaire</t>
+  </si>
+  <si>
+    <t>savoirFAire : Prérogatives d'exercice d'un professionnel reconnues par une autorité d'enregistrement sur une période donnée de son exercice professionnel, par exemple les spécialités ordinales, etc.</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.coding:typeSavoirFaire</t>
+  </si>
+  <si>
+    <t>typeSavoirFaire</t>
+  </si>
+  <si>
+    <t>Le type de savoir-faire (qualifications/autres attributions).
+typeSavoirFaire</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J91-TypeSavoirFaire-RASS/FHIR/JDV-J91-TypeSavoirFaire-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.coding:savoirFaire</t>
+  </si>
+  <si>
+    <t>Compétence acquise par le professionnel (competence) R39 ou Compétence exclusive exercée par le professionnel à titre exclusif (competenceExclusive) R40 ou Diplôme d'études spécialisées complémentaires (DESC)DESCnonQualifian R42 ou Capacité (savoir-faire)de médecine (capaciteSavoirFaire) R43 ou Qualification de praticien adjoint contractuel (qualificationPAC) R44 ou Fonction qualifiée (Synonyme: fonctionQualifiee) R45 ou Droit d'exercice complémentaire (Synonyme: droitExerciceComplementaire) R97 ou Orientation particulière (Synonyme: orientationParticuliere) G13 ou Activité ponctuelle du professionnel de type expertise (attributionParticuliere) G13.</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J107-EnsembleSavoirFaire-RASS/FHIR/JDV-J107-EnsembleSavoirFaire-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.issuer</t>
   </si>
   <si>
     <t>Practitioner.communication</t>
@@ -1691,6 +1907,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1872,12 +2103,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN83"/>
+  <dimension ref="A1:AN125"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.38671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="65.296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.38671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="19.15625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1900,7 +2131,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="97.73828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="107.80859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2038,7 +2269,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -2150,7 +2381,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>88</v>
       </c>
@@ -2264,7 +2495,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>96</v>
       </c>
@@ -2376,7 +2607,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>104</v>
       </c>
@@ -2488,7 +2719,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>110</v>
       </c>
@@ -2602,7 +2833,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>121</v>
       </c>
@@ -2716,7 +2947,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>126</v>
       </c>
@@ -2830,7 +3061,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -2944,7 +3175,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>138</v>
       </c>
@@ -3058,7 +3289,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>146</v>
       </c>
@@ -3174,7 +3405,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>148</v>
       </c>
@@ -3288,7 +3519,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>159</v>
       </c>
@@ -3402,7 +3633,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>167</v>
       </c>
@@ -3516,7 +3747,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>172</v>
       </c>
@@ -3630,7 +3861,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>181</v>
       </c>
@@ -3744,7 +3975,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>189</v>
       </c>
@@ -3858,7 +4089,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>196</v>
       </c>
@@ -3972,7 +4203,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>199</v>
       </c>
@@ -4086,7 +4317,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>204</v>
       </c>
@@ -4202,7 +4433,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>209</v>
       </c>
@@ -4316,7 +4547,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>220</v>
       </c>
@@ -4428,7 +4659,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>221</v>
       </c>
@@ -4542,7 +4773,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>222</v>
       </c>
@@ -4658,7 +4889,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>232</v>
       </c>
@@ -4772,7 +5003,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>241</v>
       </c>
@@ -4884,7 +5115,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>242</v>
       </c>
@@ -4998,7 +5229,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>243</v>
       </c>
@@ -5114,7 +5345,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>251</v>
       </c>
@@ -5226,7 +5457,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>252</v>
       </c>
@@ -5340,7 +5571,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>253</v>
       </c>
@@ -5456,7 +5687,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>262</v>
       </c>
@@ -5570,7 +5801,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>269</v>
       </c>
@@ -5686,7 +5917,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>277</v>
       </c>
@@ -5802,7 +6033,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>284</v>
       </c>
@@ -5918,7 +6149,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>293</v>
       </c>
@@ -6034,7 +6265,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>301</v>
       </c>
@@ -6150,7 +6381,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>311</v>
       </c>
@@ -6264,7 +6495,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>320</v>
       </c>
@@ -6378,7 +6609,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>330</v>
       </c>
@@ -6492,7 +6723,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>340</v>
       </c>
@@ -6608,7 +6839,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>343</v>
       </c>
@@ -6720,7 +6951,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>344</v>
       </c>
@@ -6834,7 +7065,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>345</v>
       </c>
@@ -6950,7 +7181,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>346</v>
       </c>
@@ -7066,7 +7297,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>351</v>
       </c>
@@ -7182,7 +7413,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>354</v>
       </c>
@@ -7296,7 +7527,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>356</v>
       </c>
@@ -7410,7 +7641,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>357</v>
       </c>
@@ -7524,7 +7755,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>358</v>
       </c>
@@ -7640,7 +7871,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>361</v>
       </c>
@@ -7752,7 +7983,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>362</v>
       </c>
@@ -7866,7 +8097,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>363</v>
       </c>
@@ -7982,7 +8213,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>364</v>
       </c>
@@ -8098,7 +8329,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>366</v>
       </c>
@@ -8214,7 +8445,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>368</v>
       </c>
@@ -8328,7 +8559,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>369</v>
       </c>
@@ -8442,7 +8673,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>370</v>
       </c>
@@ -8556,7 +8787,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>371</v>
       </c>
@@ -8672,7 +8903,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>374</v>
       </c>
@@ -8784,7 +9015,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>375</v>
       </c>
@@ -8898,7 +9129,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>376</v>
       </c>
@@ -9014,7 +9245,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>377</v>
       </c>
@@ -9130,7 +9361,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>379</v>
       </c>
@@ -9246,7 +9477,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>381</v>
       </c>
@@ -9360,7 +9591,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>382</v>
       </c>
@@ -9474,7 +9705,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>383</v>
       </c>
@@ -9588,7 +9819,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>384</v>
       </c>
@@ -9706,7 +9937,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>392</v>
       </c>
@@ -9822,7 +10053,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>401</v>
       </c>
@@ -9938,7 +10169,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
         <v>411</v>
       </c>
@@ -10054,7 +10285,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
         <v>420</v>
       </c>
@@ -10170,7 +10401,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
         <v>429</v>
       </c>
@@ -10284,7 +10515,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
         <v>437</v>
       </c>
@@ -10400,7 +10631,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
         <v>447</v>
       </c>
@@ -10419,7 +10650,7 @@
         <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>78</v>
@@ -10473,16 +10704,14 @@
         <v>78</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>447</v>
@@ -10500,24 +10729,24 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10624,12 +10853,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10738,16 +10967,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10769,10 +10998,10 @@
         <v>112</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>115</v>
@@ -10827,7 +11056,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10854,12 +11083,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10885,14 +11114,14 @@
         <v>210</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -10941,7 +11170,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -10956,24 +11185,24 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10999,13 +11228,13 @@
         <v>233</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11031,11 +11260,13 @@
         <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y80" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="Z80" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -11053,7 +11284,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>89</v>
@@ -11068,24 +11299,24 @@
         <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11111,16 +11342,16 @@
         <v>321</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>324</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
@@ -11169,7 +11400,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11184,24 +11415,24 @@
         <v>326</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11227,13 +11458,13 @@
         <v>331</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11283,7 +11514,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11301,7 +11532,7 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -11310,14 +11541,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C83" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>490</v>
+      </c>
       <c r="D83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11329,7 +11562,7 @@
         <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>78</v>
@@ -11338,20 +11571,16 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>233</v>
+        <v>448</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11375,13 +11604,13 @@
         <v>78</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
@@ -11399,7 +11628,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>487</v>
+        <v>447</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11414,19 +11643,4845 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AL83" t="s" s="2">
+      <c r="B84" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AM83" t="s" s="2">
+      <c r="B85" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="AN83" t="s" s="2">
+      <c r="B86" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="P87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AC91" s="2"/>
+      <c r="AD91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C92" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="D92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Y92" s="2"/>
+      <c r="Z92" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C93" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="D93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Y93" s="2"/>
+      <c r="Z93" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="D97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AC105" s="2"/>
+      <c r="AD105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="D106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Y106" s="2"/>
+      <c r="Z106" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="D107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Y107" s="2"/>
+      <c r="Z107" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="P108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O110" s="2"/>
+      <c r="P110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="D111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
+      <c r="P111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
+      <c r="P112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="P114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="P115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O118" s="2"/>
+      <c r="P118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AC119" s="2"/>
+      <c r="AD119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="D120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Y120" s="2"/>
+      <c r="Z120" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="D121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Y121" s="2"/>
+      <c r="Z121" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="P122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="P123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN125">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI124">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -9,9 +9,6 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$125</definedName>
-  </definedNames>
 </workbook>
 </file>
 
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1907,21 +1904,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -2269,7 +2251,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -2381,7 +2363,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>88</v>
       </c>
@@ -2495,7 +2477,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>96</v>
       </c>
@@ -2607,7 +2589,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>104</v>
       </c>
@@ -2719,7 +2701,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>110</v>
       </c>
@@ -2833,7 +2815,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>121</v>
       </c>
@@ -2947,7 +2929,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>126</v>
       </c>
@@ -3061,7 +3043,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -3175,7 +3157,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>138</v>
       </c>
@@ -3289,7 +3271,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>146</v>
       </c>
@@ -3405,7 +3387,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>148</v>
       </c>
@@ -3519,7 +3501,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>159</v>
       </c>
@@ -3633,7 +3615,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>167</v>
       </c>
@@ -3747,7 +3729,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>172</v>
       </c>
@@ -3861,7 +3843,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>181</v>
       </c>
@@ -3975,7 +3957,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>189</v>
       </c>
@@ -4089,7 +4071,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>196</v>
       </c>
@@ -4203,7 +4185,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>199</v>
       </c>
@@ -4317,7 +4299,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>204</v>
       </c>
@@ -4433,7 +4415,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>209</v>
       </c>
@@ -4547,7 +4529,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>220</v>
       </c>
@@ -4659,7 +4641,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>221</v>
       </c>
@@ -4773,7 +4755,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>222</v>
       </c>
@@ -4889,7 +4871,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>232</v>
       </c>
@@ -5003,7 +4985,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>241</v>
       </c>
@@ -5115,7 +5097,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>242</v>
       </c>
@@ -5229,7 +5211,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>243</v>
       </c>
@@ -5345,7 +5327,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>251</v>
       </c>
@@ -5457,7 +5439,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>252</v>
       </c>
@@ -5571,7 +5553,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>253</v>
       </c>
@@ -5687,7 +5669,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>262</v>
       </c>
@@ -5801,7 +5783,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>269</v>
       </c>
@@ -5917,7 +5899,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>277</v>
       </c>
@@ -6033,7 +6015,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>284</v>
       </c>
@@ -6149,7 +6131,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>293</v>
       </c>
@@ -6265,7 +6247,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>301</v>
       </c>
@@ -6381,7 +6363,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>311</v>
       </c>
@@ -6495,7 +6477,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>320</v>
       </c>
@@ -6609,7 +6591,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>330</v>
       </c>
@@ -6723,7 +6705,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>340</v>
       </c>
@@ -6839,7 +6821,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>343</v>
       </c>
@@ -6951,7 +6933,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>344</v>
       </c>
@@ -7065,7 +7047,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>345</v>
       </c>
@@ -7181,7 +7163,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>346</v>
       </c>
@@ -7297,7 +7279,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>351</v>
       </c>
@@ -7413,7 +7395,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>354</v>
       </c>
@@ -7527,7 +7509,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>356</v>
       </c>
@@ -7641,7 +7623,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>357</v>
       </c>
@@ -7755,7 +7737,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>358</v>
       </c>
@@ -7871,7 +7853,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>361</v>
       </c>
@@ -7983,7 +7965,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>362</v>
       </c>
@@ -8097,7 +8079,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>363</v>
       </c>
@@ -8213,7 +8195,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>364</v>
       </c>
@@ -8329,7 +8311,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>366</v>
       </c>
@@ -8445,7 +8427,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>368</v>
       </c>
@@ -8559,7 +8541,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
         <v>369</v>
       </c>
@@ -8673,7 +8655,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>370</v>
       </c>
@@ -8787,7 +8769,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>371</v>
       </c>
@@ -8903,7 +8885,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>374</v>
       </c>
@@ -9015,7 +8997,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>375</v>
       </c>
@@ -9129,7 +9111,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>376</v>
       </c>
@@ -9245,7 +9227,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>377</v>
       </c>
@@ -9361,7 +9343,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>379</v>
       </c>
@@ -9477,7 +9459,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>381</v>
       </c>
@@ -9591,7 +9573,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>382</v>
       </c>
@@ -9705,7 +9687,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>383</v>
       </c>
@@ -9819,7 +9801,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>384</v>
       </c>
@@ -9937,7 +9919,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
         <v>392</v>
       </c>
@@ -10053,7 +10035,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>401</v>
       </c>
@@ -10169,7 +10151,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>411</v>
       </c>
@@ -10285,7 +10267,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>420</v>
       </c>
@@ -10401,7 +10383,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>429</v>
       </c>
@@ -10515,7 +10497,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
         <v>437</v>
       </c>
@@ -10631,7 +10613,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
         <v>447</v>
       </c>
@@ -10650,7 +10632,7 @@
         <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>78</v>
@@ -10741,7 +10723,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
         <v>455</v>
       </c>
@@ -10853,7 +10835,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
         <v>456</v>
       </c>
@@ -10967,7 +10949,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>457</v>
       </c>
@@ -11083,7 +11065,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
         <v>462</v>
       </c>
@@ -11197,7 +11179,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
         <v>469</v>
       </c>
@@ -11311,7 +11293,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>477</v>
       </c>
@@ -11427,7 +11409,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
         <v>484</v>
       </c>
@@ -11541,7 +11523,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
         <v>489</v>
       </c>
@@ -11562,7 +11544,7 @@
         <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>78</v>
@@ -11655,7 +11637,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
         <v>492</v>
       </c>
@@ -11767,7 +11749,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
         <v>493</v>
       </c>
@@ -11881,7 +11863,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
         <v>494</v>
       </c>
@@ -11997,7 +11979,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>495</v>
       </c>
@@ -12111,7 +12093,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
         <v>496</v>
       </c>
@@ -12225,7 +12207,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
         <v>497</v>
       </c>
@@ -12337,7 +12319,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
         <v>499</v>
       </c>
@@ -12451,7 +12433,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
         <v>501</v>
       </c>
@@ -12565,7 +12547,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
         <v>505</v>
       </c>
@@ -12586,7 +12568,7 @@
         <v>89</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>78</v>
@@ -12681,7 +12663,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
         <v>508</v>
       </c>
@@ -12702,7 +12684,7 @@
         <v>89</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>78</v>
@@ -12797,7 +12779,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>510</v>
       </c>
@@ -12913,7 +12895,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
         <v>512</v>
       </c>
@@ -13029,7 +13011,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
         <v>513</v>
       </c>
@@ -13143,7 +13125,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
         <v>514</v>
       </c>
@@ -13257,7 +13239,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
         <v>517</v>
       </c>
@@ -13369,7 +13351,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
         <v>518</v>
       </c>
@@ -13483,7 +13465,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
         <v>519</v>
       </c>
@@ -13599,7 +13581,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
         <v>520</v>
       </c>
@@ -13713,7 +13695,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
         <v>521</v>
       </c>
@@ -13827,7 +13809,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
         <v>522</v>
       </c>
@@ -13939,7 +13921,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>523</v>
       </c>
@@ -14053,7 +14035,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
         <v>524</v>
       </c>
@@ -14167,7 +14149,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
         <v>525</v>
       </c>
@@ -14188,7 +14170,7 @@
         <v>89</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>78</v>
@@ -14283,7 +14265,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
         <v>529</v>
       </c>
@@ -14304,7 +14286,7 @@
         <v>89</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>78</v>
@@ -14399,7 +14381,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
         <v>533</v>
       </c>
@@ -14515,7 +14497,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
         <v>534</v>
       </c>
@@ -14631,7 +14613,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
         <v>535</v>
       </c>
@@ -14745,7 +14727,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
         <v>536</v>
       </c>
@@ -14859,7 +14841,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="112" hidden="true">
+    <row r="112">
       <c r="A112" t="s" s="2">
         <v>539</v>
       </c>
@@ -14971,7 +14953,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
         <v>540</v>
       </c>
@@ -15085,7 +15067,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="114" hidden="true">
+    <row r="114">
       <c r="A114" t="s" s="2">
         <v>541</v>
       </c>
@@ -15201,7 +15183,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
         <v>542</v>
       </c>
@@ -15315,7 +15297,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="116" hidden="true">
+    <row r="116">
       <c r="A116" t="s" s="2">
         <v>543</v>
       </c>
@@ -15429,7 +15411,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
         <v>544</v>
       </c>
@@ -15541,7 +15523,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
         <v>545</v>
       </c>
@@ -15655,7 +15637,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="119" hidden="true">
+    <row r="119">
       <c r="A119" t="s" s="2">
         <v>546</v>
       </c>
@@ -15769,7 +15751,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="120" hidden="true">
+    <row r="120">
       <c r="A120" t="s" s="2">
         <v>547</v>
       </c>
@@ -15790,7 +15772,7 @@
         <v>89</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>78</v>
@@ -15885,7 +15867,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="121" hidden="true">
+    <row r="121">
       <c r="A121" t="s" s="2">
         <v>551</v>
       </c>
@@ -15906,7 +15888,7 @@
         <v>89</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>78</v>
@@ -16001,7 +15983,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
         <v>554</v>
       </c>
@@ -16117,7 +16099,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
         <v>555</v>
       </c>
@@ -16233,7 +16215,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
         <v>556</v>
       </c>
@@ -16347,7 +16329,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="125" hidden="true">
+    <row r="125">
       <c r="A125" t="s" s="2">
         <v>557</v>
       </c>
@@ -16464,24 +16446,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN125">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI124">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,8 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>French profile of the Practitioner resource. This profile specifies the types of identifiers for practitioners in France.
-Profil de la ressource Practitionner pour la France. Ce profil contraint les types d'identifiants du professionnel de santé en France</t>
+    <t>Profil de la ressource Practitionner pour la France.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -263,10 +262,10 @@
 </t>
   </si>
   <si>
-    <t>A person with a  formal responsibility in the provisioning of healthcare or related services | Prestataire de santé</t>
-  </si>
-  <si>
-    <t>A person who is directly or indirectly involved in the provisioning of healthcare | Un professionnel impliqué directement ou indirectement dans la prise en charge d'une personne.</t>
+    <t>A person with a  formal responsibility in the provisioning of healthcare or related services</t>
+  </si>
+  <si>
+    <t>A person who is directly or indirectly involved in the provisioning of healthcare.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -426,7 +426,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -446,7 +446,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -1300,7 +1300,7 @@
     <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
   </si>
   <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
+    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
   </si>
   <si>
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>89</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>89</v>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>89</v>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>89</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>89</v>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>89</v>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>89</v>
@@ -8377,7 +8377,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>89</v>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>89</v>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>89</v>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>89</v>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4550" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4224" uniqueCount="537">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1157,50 +1157,6 @@
   </si>
   <si>
     <t>Practitioner.identifier:rpps.assigner</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:adeli</t>
-  </si>
-  <si>
-    <t>adeli</t>
-  </si>
-  <si>
-    <t>Numéro ADELI (9 chiffres)</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:adeli.id</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:adeli.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:adeli.use</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:adeli.type</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
-    &lt;code value="ADELI"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:adeli.system</t>
-  </si>
-  <si>
-    <t>https://adeli.esante.gouv.fr</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:adeli.value</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:adeli.period</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:adeli.assigner</t>
   </si>
   <si>
     <t>Practitioner.active</t>
@@ -2034,7 +1990,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN125"/>
+  <dimension ref="A1:AN116"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="65.296875" customWidth="true" bestFit="true"/>
@@ -8709,11 +8665,9 @@
         <v>366</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>78</v>
       </c>
@@ -8722,7 +8676,7 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
@@ -8734,22 +8688,26 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>209</v>
+        <v>283</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N59" s="2"/>
+      <c r="N59" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="O59" t="s" s="2">
-        <v>212</v>
+        <v>370</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q59" s="2"/>
+      <c r="Q59" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="R59" t="s" s="2">
         <v>78</v>
       </c>
@@ -8793,13 +8751,13 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>208</v>
+        <v>366</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>78</v>
@@ -8808,24 +8766,24 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>216</v>
+        <v>372</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>217</v>
+        <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>218</v>
+        <v>373</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>219</v>
+        <v>374</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8836,7 +8794,7 @@
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -8848,16 +8806,20 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>103</v>
+        <v>375</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>104</v>
+        <v>376</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
       </c>
@@ -8905,28 +8867,28 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>106</v>
+        <v>374</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>107</v>
+        <v>381</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>78</v>
+        <v>382</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8934,14 +8896,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>220</v>
+        <v>383</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8960,18 +8922,20 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>110</v>
+        <v>384</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>111</v>
+        <v>385</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>112</v>
+        <v>386</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
@@ -9007,19 +8971,19 @@
         <v>78</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>117</v>
+        <v>383</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9028,19 +8992,19 @@
         <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>118</v>
+        <v>389</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>78</v>
+        <v>390</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>107</v>
+        <v>391</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -9048,10 +9012,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>221</v>
+        <v>393</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9062,31 +9026,31 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>169</v>
+        <v>394</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>222</v>
+        <v>395</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>223</v>
+        <v>396</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>224</v>
+        <v>397</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>225</v>
+        <v>398</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
@@ -9111,13 +9075,13 @@
         <v>78</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>227</v>
+        <v>78</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
@@ -9135,28 +9099,28 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>229</v>
+        <v>393</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>192</v>
+        <v>399</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>230</v>
+        <v>400</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>78</v>
+        <v>401</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9164,10 +9128,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>372</v>
+        <v>402</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>231</v>
+        <v>402</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9175,7 +9139,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>89</v>
@@ -9190,19 +9154,17 @@
         <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>232</v>
+        <v>169</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>233</v>
+        <v>403</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>236</v>
+        <v>405</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9212,7 +9174,7 @@
         <v>78</v>
       </c>
       <c r="S63" t="s" s="2">
-        <v>373</v>
+        <v>78</v>
       </c>
       <c r="T63" t="s" s="2">
         <v>78</v>
@@ -9227,13 +9189,13 @@
         <v>78</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>344</v>
+        <v>406</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>345</v>
+        <v>407</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
@@ -9251,7 +9213,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>238</v>
+        <v>402</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9266,13 +9228,13 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>239</v>
+        <v>408</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>230</v>
+        <v>409</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9280,10 +9242,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>374</v>
+        <v>411</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>299</v>
+        <v>411</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9291,7 +9253,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>89</v>
@@ -9306,19 +9268,17 @@
         <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>131</v>
+        <v>412</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>300</v>
+        <v>413</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>303</v>
+        <v>415</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9328,10 +9288,10 @@
         <v>78</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>375</v>
+        <v>78</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>304</v>
+        <v>78</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>78</v>
@@ -9367,7 +9327,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>305</v>
+        <v>411</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9382,13 +9342,13 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>306</v>
+        <v>416</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>307</v>
+        <v>417</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>308</v>
+        <v>418</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9396,10 +9356,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>376</v>
+        <v>419</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>309</v>
+        <v>419</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9407,10 +9367,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>78</v>
@@ -9419,21 +9379,21 @@
         <v>78</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>103</v>
+        <v>420</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>310</v>
+        <v>421</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9445,7 +9405,7 @@
         <v>78</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>313</v>
+        <v>78</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>78</v>
@@ -9481,13 +9441,13 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>314</v>
+        <v>419</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>78</v>
@@ -9496,13 +9456,13 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>315</v>
+        <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>316</v>
+        <v>424</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>317</v>
+        <v>425</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
@@ -9510,10 +9470,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>377</v>
+        <v>426</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>318</v>
+        <v>426</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9524,7 +9484,7 @@
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
@@ -9533,16 +9493,16 @@
         <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>319</v>
+        <v>427</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>320</v>
+        <v>428</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>321</v>
+        <v>429</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9581,25 +9541,23 @@
         <v>78</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="AC66" s="2"/>
       <c r="AD66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>322</v>
+        <v>426</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>78</v>
@@ -9608,13 +9566,13 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>323</v>
+        <v>431</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>324</v>
+        <v>432</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>325</v>
+        <v>433</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>78</v>
@@ -9622,10 +9580,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>378</v>
+        <v>434</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>326</v>
+        <v>434</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9645,20 +9603,18 @@
         <v>78</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>327</v>
+        <v>103</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>328</v>
+        <v>104</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -9707,7 +9663,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>331</v>
+        <v>106</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9719,16 +9675,16 @@
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>333</v>
+        <v>107</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>334</v>
+        <v>78</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>78</v>
@@ -9736,21 +9692,21 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>379</v>
+        <v>435</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>379</v>
+        <v>435</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>78</v>
@@ -9759,29 +9715,25 @@
         <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>283</v>
+        <v>110</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>380</v>
+        <v>111</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>381</v>
+        <v>112</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q68" t="s" s="2">
-        <v>384</v>
-      </c>
+      <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
         <v>78</v>
       </c>
@@ -9825,43 +9777,43 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>379</v>
+        <v>117</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>385</v>
+        <v>107</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>386</v>
+        <v>78</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>387</v>
+        <v>436</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>387</v>
+        <v>436</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>78</v>
+        <v>437</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9874,25 +9826,25 @@
         <v>78</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>388</v>
+        <v>110</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>389</v>
+        <v>438</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>390</v>
+        <v>439</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>391</v>
+        <v>113</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>392</v>
+        <v>206</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -9941,7 +9893,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>387</v>
+        <v>440</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9950,19 +9902,19 @@
         <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>202</v>
+        <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>393</v>
+        <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>394</v>
+        <v>192</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>395</v>
+        <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
@@ -9970,10 +9922,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>396</v>
+        <v>441</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>396</v>
+        <v>441</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9996,19 +9948,17 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>397</v>
+        <v>209</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>398</v>
+        <v>442</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>401</v>
+        <v>444</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -10057,7 +10007,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>396</v>
+        <v>441</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10066,19 +10016,19 @@
         <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>202</v>
+        <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>402</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>404</v>
+        <v>445</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>405</v>
+        <v>78</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
@@ -10086,10 +10036,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>406</v>
+        <v>446</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>406</v>
+        <v>446</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10097,10 +10047,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>78</v>
@@ -10112,20 +10062,16 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>407</v>
+        <v>232</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
@@ -10149,13 +10095,13 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>78</v>
+        <v>449</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>78</v>
+        <v>450</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -10173,28 +10119,28 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>406</v>
+        <v>446</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>202</v>
+        <v>78</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>412</v>
+        <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>414</v>
+        <v>451</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -10202,10 +10148,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>415</v>
+        <v>452</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>415</v>
+        <v>452</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10225,20 +10171,20 @@
         <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>169</v>
+        <v>319</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>416</v>
+        <v>453</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>417</v>
+        <v>454</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>418</v>
+        <v>455</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10263,13 +10209,13 @@
         <v>78</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>419</v>
+        <v>78</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -10287,7 +10233,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>415</v>
+        <v>452</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10302,13 +10248,13 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>421</v>
+        <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>422</v>
+        <v>456</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>423</v>
+        <v>457</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10316,10 +10262,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>424</v>
+        <v>458</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>424</v>
+        <v>458</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10339,21 +10285,19 @@
         <v>78</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>425</v>
+        <v>327</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>426</v>
+        <v>459</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>427</v>
+        <v>460</v>
       </c>
       <c r="N73" s="2"/>
-      <c r="O73" t="s" s="2">
-        <v>428</v>
-      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10401,7 +10345,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>424</v>
+        <v>458</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10416,13 +10360,13 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>429</v>
+        <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>430</v>
+        <v>461</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>431</v>
+        <v>78</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10430,12 +10374,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>432</v>
+        <v>462</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C74" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="D74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10456,18 +10402,16 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>434</v>
+        <v>464</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="N74" s="2"/>
-      <c r="O74" t="s" s="2">
-        <v>436</v>
-      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10515,7 +10459,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10530,13 +10474,13 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>78</v>
+        <v>431</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10544,10 +10488,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10558,7 +10502,7 @@
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
@@ -10570,13 +10514,13 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>440</v>
+        <v>103</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>441</v>
+        <v>104</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>442</v>
+        <v>105</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10615,38 +10559,40 @@
         <v>78</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AC75" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>439</v>
+        <v>106</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>444</v>
+        <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>445</v>
+        <v>107</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>446</v>
+        <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -10654,21 +10600,21 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>78</v>
@@ -10680,15 +10626,17 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -10737,19 +10685,19 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
@@ -10766,14 +10714,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>109</v>
+        <v>437</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10786,24 +10734,26 @@
         <v>78</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>111</v>
+        <v>438</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>112</v>
+        <v>439</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>78</v>
       </c>
@@ -10851,7 +10801,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>117</v>
+        <v>440</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10869,7 +10819,7 @@
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>78</v>
@@ -10880,14 +10830,14 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>450</v>
+        <v>78</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10900,25 +10850,23 @@
         <v>78</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>110</v>
+        <v>209</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>206</v>
+        <v>444</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -10967,7 +10915,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10979,13 +10927,13 @@
         <v>78</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>192</v>
+        <v>445</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>78</v>
@@ -10996,10 +10944,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11007,10 +10955,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>78</v>
@@ -11022,18 +10970,16 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="N79" s="2"/>
-      <c r="O79" t="s" s="2">
-        <v>457</v>
-      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>78</v>
       </c>
@@ -11057,13 +11003,13 @@
         <v>78</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>78</v>
+        <v>449</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>78</v>
+        <v>450</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>78</v>
@@ -11081,13 +11027,13 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>78</v>
@@ -11099,10 +11045,10 @@
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>458</v>
+        <v>432</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>78</v>
+        <v>451</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -11110,10 +11056,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11121,7 +11067,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>89</v>
@@ -11136,13 +11082,13 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>232</v>
+        <v>103</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>460</v>
+        <v>104</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>461</v>
+        <v>105</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11169,13 +11115,13 @@
         <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>462</v>
+        <v>78</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>463</v>
+        <v>78</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -11193,10 +11139,10 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>459</v>
+        <v>106</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>89</v>
@@ -11205,16 +11151,16 @@
         <v>78</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>445</v>
+        <v>107</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>464</v>
+        <v>78</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11222,21 +11168,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>78</v>
@@ -11248,18 +11194,18 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>319</v>
+        <v>110</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>466</v>
+        <v>111</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>78</v>
       </c>
@@ -11295,40 +11241,40 @@
         <v>78</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>465</v>
+        <v>117</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>469</v>
+        <v>107</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>470</v>
+        <v>78</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -11336,10 +11282,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11350,7 +11296,7 @@
         <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>78</v>
@@ -11359,19 +11305,23 @@
         <v>78</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>327</v>
+        <v>147</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>472</v>
+        <v>243</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
       </c>
@@ -11407,25 +11357,23 @@
         <v>78</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC82" s="2"/>
       <c r="AD82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>78</v>
+        <v>476</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>471</v>
+        <v>247</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>78</v>
@@ -11434,10 +11382,10 @@
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>474</v>
+        <v>249</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -11448,13 +11396,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="B83" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="C83" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D83" t="s" s="2">
         <v>78</v>
@@ -11464,7 +11412,7 @@
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>78</v>
@@ -11473,19 +11421,23 @@
         <v>78</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>440</v>
+        <v>147</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>477</v>
+        <v>243</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11509,13 +11461,11 @@
         <v>78</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>78</v>
+        <v>479</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
@@ -11533,7 +11483,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>439</v>
+        <v>247</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11548,13 +11498,13 @@
         <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>444</v>
+        <v>248</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>445</v>
+        <v>249</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>446</v>
+        <v>78</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>78</v>
@@ -11562,12 +11512,14 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C84" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="C84" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="D84" t="s" s="2">
         <v>78</v>
       </c>
@@ -11585,19 +11537,23 @@
         <v>78</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>104</v>
+        <v>243</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
       </c>
@@ -11621,13 +11577,11 @@
         <v>78</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>78</v>
+        <v>481</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>78</v>
@@ -11645,25 +11599,25 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>106</v>
+        <v>247</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>107</v>
+        <v>249</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
@@ -11674,21 +11628,21 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>448</v>
+        <v>483</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>78</v>
@@ -11697,21 +11651,23 @@
         <v>78</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>111</v>
+        <v>292</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>112</v>
+        <v>293</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>78</v>
       </c>
@@ -11759,25 +11715,25 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>117</v>
+        <v>296</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>78</v>
+        <v>297</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>107</v>
+        <v>298</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>78</v>
@@ -11788,45 +11744,43 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>450</v>
+        <v>78</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>110</v>
+        <v>319</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>206</v>
+        <v>455</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>78</v>
@@ -11875,28 +11829,28 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>192</v>
+        <v>456</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -11904,10 +11858,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11918,7 +11872,7 @@
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>78</v>
@@ -11930,18 +11884,16 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>209</v>
+        <v>327</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="N87" s="2"/>
-      <c r="O87" t="s" s="2">
-        <v>457</v>
-      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>78</v>
       </c>
@@ -11989,13 +11941,13 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>78</v>
@@ -12007,7 +11959,7 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -12018,18 +11970,20 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="C88" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>487</v>
+      </c>
       <c r="D88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>89</v>
@@ -12044,13 +11998,13 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>232</v>
+        <v>427</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>460</v>
+        <v>488</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>461</v>
+        <v>429</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12077,13 +12031,13 @@
         <v>78</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>462</v>
+        <v>78</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>463</v>
+        <v>78</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>78</v>
@@ -12101,13 +12055,13 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>459</v>
+        <v>426</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>78</v>
@@ -12116,13 +12070,13 @@
         <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>78</v>
+        <v>431</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>464</v>
+        <v>433</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>78</v>
@@ -12130,10 +12084,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>484</v>
+        <v>434</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12242,10 +12196,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>486</v>
+        <v>435</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12315,16 +12269,16 @@
         <v>78</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
         <v>117</v>
@@ -12356,14 +12310,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>488</v>
+        <v>436</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>78</v>
+        <v>437</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -12376,25 +12330,25 @@
         <v>78</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J91" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>243</v>
+        <v>438</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>244</v>
+        <v>439</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>245</v>
+        <v>113</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -12431,17 +12385,19 @@
         <v>78</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AC91" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>489</v>
+        <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>247</v>
+        <v>440</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12453,13 +12409,13 @@
         <v>78</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>249</v>
+        <v>192</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
@@ -12470,14 +12426,12 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C92" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
         <v>78</v>
       </c>
@@ -12486,7 +12440,7 @@
         <v>79</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>78</v>
@@ -12495,22 +12449,20 @@
         <v>78</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>147</v>
+        <v>209</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>243</v>
+        <v>442</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>246</v>
+        <v>444</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -12535,11 +12487,13 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y92" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z92" t="s" s="2">
-        <v>492</v>
+        <v>78</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -12557,7 +12511,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>247</v>
+        <v>441</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12572,10 +12526,10 @@
         <v>101</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>249</v>
+        <v>445</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -12589,17 +12543,15 @@
         <v>493</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>476</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>89</v>
@@ -12611,23 +12563,19 @@
         <v>78</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>147</v>
+        <v>232</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>243</v>
+        <v>447</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>78</v>
       </c>
@@ -12651,11 +12599,13 @@
         <v>78</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y93" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="Z93" t="s" s="2">
-        <v>494</v>
+        <v>450</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>78</v>
@@ -12673,13 +12623,13 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>247</v>
+        <v>446</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>78</v>
@@ -12688,13 +12638,13 @@
         <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>249</v>
+        <v>432</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>78</v>
+        <v>451</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -12702,10 +12652,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>496</v>
+        <v>471</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12725,23 +12675,19 @@
         <v>78</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>292</v>
+        <v>104</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>78</v>
       </c>
@@ -12789,7 +12735,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>296</v>
+        <v>106</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -12801,13 +12747,13 @@
         <v>78</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>297</v>
+        <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>298</v>
+        <v>107</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
@@ -12818,21 +12764,21 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>78</v>
@@ -12844,18 +12790,18 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>319</v>
+        <v>110</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>466</v>
+        <v>111</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>78</v>
       </c>
@@ -12891,40 +12837,40 @@
         <v>78</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>465</v>
+        <v>117</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>469</v>
+        <v>107</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>470</v>
+        <v>78</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
@@ -12932,10 +12878,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12946,7 +12892,7 @@
         <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>78</v>
@@ -12955,19 +12901,23 @@
         <v>78</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>327</v>
+        <v>147</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>472</v>
+        <v>243</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>78</v>
       </c>
@@ -13003,25 +12953,23 @@
         <v>78</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC96" s="2"/>
       <c r="AD96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>78</v>
+        <v>476</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>471</v>
+        <v>247</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>78</v>
@@ -13030,10 +12978,10 @@
         <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>474</v>
+        <v>249</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13044,13 +12992,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>439</v>
+        <v>475</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>78</v>
@@ -13069,19 +13017,23 @@
         <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>440</v>
+        <v>147</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
       </c>
@@ -13105,13 +13057,11 @@
         <v>78</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>78</v>
+        <v>500</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>78</v>
@@ -13129,7 +13079,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>439</v>
+        <v>247</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13144,13 +13094,13 @@
         <v>101</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>444</v>
+        <v>248</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>445</v>
+        <v>249</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>446</v>
+        <v>78</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>78</v>
@@ -13158,12 +13108,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C98" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="B98" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>78</v>
       </c>
@@ -13181,19 +13133,23 @@
         <v>78</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>104</v>
+        <v>503</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>78</v>
       </c>
@@ -13217,13 +13173,11 @@
         <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>78</v>
+        <v>504</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>78</v>
@@ -13241,25 +13195,25 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>106</v>
+        <v>247</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>107</v>
+        <v>249</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
@@ -13270,21 +13224,21 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>448</v>
+        <v>483</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>78</v>
@@ -13293,21 +13247,23 @@
         <v>78</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>111</v>
+        <v>292</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>112</v>
+        <v>293</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
       </c>
@@ -13355,25 +13311,25 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>117</v>
+        <v>296</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>78</v>
+        <v>297</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>107</v>
+        <v>298</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>78</v>
@@ -13384,45 +13340,43 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>450</v>
+        <v>78</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>110</v>
+        <v>319</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>206</v>
+        <v>455</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -13471,28 +13425,28 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>192</v>
+        <v>456</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -13500,10 +13454,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13514,7 +13468,7 @@
         <v>79</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
@@ -13526,18 +13480,16 @@
         <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>209</v>
+        <v>327</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="N101" s="2"/>
-      <c r="O101" t="s" s="2">
-        <v>457</v>
-      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>78</v>
       </c>
@@ -13585,13 +13537,13 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>78</v>
@@ -13603,7 +13555,7 @@
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
@@ -13614,21 +13566,23 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="C102" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>509</v>
+      </c>
       <c r="D102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>78</v>
@@ -13640,13 +13594,13 @@
         <v>78</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>232</v>
+        <v>427</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>460</v>
+        <v>510</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>461</v>
+        <v>429</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13673,13 +13627,13 @@
         <v>78</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>462</v>
+        <v>78</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>463</v>
+        <v>78</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>78</v>
@@ -13697,13 +13651,13 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>459</v>
+        <v>426</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>78</v>
@@ -13712,13 +13666,13 @@
         <v>101</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>78</v>
+        <v>431</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>464</v>
+        <v>433</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>78</v>
@@ -13726,10 +13680,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>484</v>
+        <v>434</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13838,10 +13792,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>486</v>
+        <v>435</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13911,16 +13865,16 @@
         <v>78</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>117</v>
@@ -13952,14 +13906,14 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>488</v>
+        <v>436</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>78</v>
+        <v>437</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -13972,25 +13926,25 @@
         <v>78</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J105" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>243</v>
+        <v>438</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>244</v>
+        <v>439</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>245</v>
+        <v>113</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -14027,17 +13981,19 @@
         <v>78</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AC105" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>489</v>
+        <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>247</v>
+        <v>440</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14049,13 +14005,13 @@
         <v>78</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>249</v>
+        <v>192</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14066,14 +14022,12 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C106" t="s" s="2">
-        <v>511</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
         <v>78</v>
       </c>
@@ -14082,7 +14036,7 @@
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>78</v>
@@ -14091,22 +14045,20 @@
         <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>147</v>
+        <v>209</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>512</v>
+        <v>442</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>246</v>
+        <v>444</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>78</v>
@@ -14131,11 +14083,13 @@
         <v>78</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y106" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z106" t="s" s="2">
-        <v>513</v>
+        <v>78</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>78</v>
@@ -14153,7 +14107,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>247</v>
+        <v>441</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14168,10 +14122,10 @@
         <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>249</v>
+        <v>445</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
@@ -14182,20 +14136,18 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C107" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>89</v>
@@ -14207,23 +14159,19 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>147</v>
+        <v>232</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>516</v>
+        <v>447</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>78</v>
       </c>
@@ -14247,11 +14195,13 @@
         <v>78</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y107" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="Z107" t="s" s="2">
-        <v>517</v>
+        <v>450</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>78</v>
@@ -14269,13 +14219,13 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>247</v>
+        <v>446</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>78</v>
@@ -14284,13 +14234,13 @@
         <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>249</v>
+        <v>432</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>78</v>
+        <v>451</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>78</v>
@@ -14298,10 +14248,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>496</v>
+        <v>471</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14321,23 +14271,19 @@
         <v>78</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K108" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>292</v>
+        <v>104</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>78</v>
       </c>
@@ -14385,7 +14331,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>296</v>
+        <v>106</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14397,13 +14343,13 @@
         <v>78</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>297</v>
+        <v>78</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>298</v>
+        <v>107</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14414,21 +14360,21 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>78</v>
@@ -14440,18 +14386,18 @@
         <v>78</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>319</v>
+        <v>110</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>466</v>
+        <v>111</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>78</v>
       </c>
@@ -14487,40 +14433,40 @@
         <v>78</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>465</v>
+        <v>117</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>469</v>
+        <v>107</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>470</v>
+        <v>78</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>78</v>
@@ -14528,10 +14474,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14542,7 +14488,7 @@
         <v>79</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>78</v>
@@ -14551,19 +14497,23 @@
         <v>78</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>327</v>
+        <v>147</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>472</v>
+        <v>243</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>78</v>
       </c>
@@ -14599,25 +14549,23 @@
         <v>78</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC110" s="2"/>
       <c r="AD110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>78</v>
+        <v>476</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>471</v>
+        <v>247</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>78</v>
@@ -14626,10 +14574,10 @@
         <v>101</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>474</v>
+        <v>249</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -14640,13 +14588,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>439</v>
+        <v>475</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>78</v>
@@ -14656,7 +14604,7 @@
         <v>79</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>78</v>
@@ -14665,19 +14613,23 @@
         <v>78</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>440</v>
+        <v>147</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
       </c>
@@ -14701,13 +14653,11 @@
         <v>78</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>78</v>
+        <v>522</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>78</v>
@@ -14725,7 +14675,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>439</v>
+        <v>247</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -14740,13 +14690,13 @@
         <v>101</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>444</v>
+        <v>248</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>445</v>
+        <v>249</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>446</v>
+        <v>78</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>78</v>
@@ -14754,12 +14704,14 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C112" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="C112" t="s" s="2">
+        <v>509</v>
+      </c>
       <c r="D112" t="s" s="2">
         <v>78</v>
       </c>
@@ -14777,19 +14729,23 @@
         <v>78</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>104</v>
+        <v>524</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>78</v>
       </c>
@@ -14813,13 +14769,11 @@
         <v>78</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>78</v>
+        <v>525</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>78</v>
@@ -14837,25 +14791,25 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>106</v>
+        <v>247</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>107</v>
+        <v>249</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -14866,21 +14820,21 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>448</v>
+        <v>483</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>78</v>
@@ -14889,21 +14843,23 @@
         <v>78</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>111</v>
+        <v>292</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>112</v>
+        <v>293</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O113" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
       </c>
@@ -14951,25 +14907,25 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>117</v>
+        <v>296</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>78</v>
+        <v>297</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>107</v>
+        <v>298</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
@@ -14980,45 +14936,43 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>450</v>
+        <v>78</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>110</v>
+        <v>319</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>206</v>
+        <v>455</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>78</v>
@@ -15067,28 +15021,28 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>192</v>
+        <v>456</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>78</v>
@@ -15096,10 +15050,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15110,7 +15064,7 @@
         <v>79</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>78</v>
@@ -15122,18 +15076,16 @@
         <v>78</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>209</v>
+        <v>327</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="N115" s="2"/>
-      <c r="O115" t="s" s="2">
-        <v>457</v>
-      </c>
+      <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>78</v>
       </c>
@@ -15181,13 +15133,13 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>78</v>
@@ -15199,7 +15151,7 @@
         <v>78</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>78</v>
@@ -15210,10 +15162,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>459</v>
+        <v>529</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15221,10 +15173,10 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>78</v>
@@ -15239,13 +15191,17 @@
         <v>232</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>460</v>
+        <v>530</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
+        <v>531</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>533</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>78</v>
       </c>
@@ -15269,13 +15225,13 @@
         <v>78</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>462</v>
+        <v>174</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>463</v>
+        <v>175</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>78</v>
@@ -15293,13 +15249,13 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>459</v>
+        <v>529</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>78</v>
@@ -15308,1045 +15264,15 @@
         <v>101</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>78</v>
+        <v>534</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>445</v>
+        <v>535</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>464</v>
+        <v>536</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
-      <c r="P117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O118" s="2"/>
-      <c r="P118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="P119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AC119" s="2"/>
-      <c r="AD119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C120" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="D120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="P120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y120" s="2"/>
-      <c r="Z120" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C121" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="D121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="P121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y121" s="2"/>
-      <c r="Z121" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="P122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="P123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
-      <c r="P124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="P125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="AN125" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4224" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5018" uniqueCount="555">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1087,16 +1087,40 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>Practitioner.identifier:idNatPs.type.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.coding.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.coding.system</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.coding.version</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.coding.code</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.coding.display</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.text</t>
   </si>
   <si>
     <t>Practitioner.identifier:idNatPs.system</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>urn:oid:1.2.250.1.71.4.2.1</t>
@@ -1142,6 +1166,39 @@
     &lt;code value="RPPS"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.coding.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.coding.system</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.coding.version</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.coding.code</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.coding.display</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.text</t>
   </si>
   <si>
     <t>Practitioner.identifier:rpps.system</t>
@@ -1995,7 +2052,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN116"/>
+  <dimension ref="A1:AN138"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="65.296875" customWidth="true" bestFit="true"/>
@@ -7130,11 +7187,9 @@
       <c r="X45" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="Y45" t="s" s="2">
-        <v>344</v>
-      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>345</v>
+        <v>237</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>78</v>
@@ -7181,10 +7236,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>299</v>
+        <v>240</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7192,7 +7247,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>89</v>
@@ -7204,23 +7259,19 @@
         <v>78</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>300</v>
+        <v>104</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
@@ -7229,10 +7280,10 @@
         <v>78</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>348</v>
+        <v>78</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>304</v>
+        <v>78</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>78</v>
@@ -7268,7 +7319,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>305</v>
+        <v>106</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7280,16 +7331,16 @@
         <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>306</v>
+        <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>307</v>
+        <v>107</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>308</v>
+        <v>78</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7297,21 +7348,21 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>78</v>
@@ -7320,19 +7371,19 @@
         <v>78</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>350</v>
+        <v>111</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>311</v>
+        <v>112</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>312</v>
+        <v>113</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7346,7 +7397,7 @@
         <v>78</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>313</v>
+        <v>78</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>78</v>
@@ -7370,40 +7421,40 @@
         <v>78</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>314</v>
+        <v>117</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>315</v>
+        <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>316</v>
+        <v>107</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>317</v>
+        <v>78</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7411,10 +7462,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>318</v>
+        <v>242</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7425,7 +7476,7 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>78</v>
@@ -7437,16 +7488,20 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>319</v>
+        <v>147</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>320</v>
+        <v>243</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
       </c>
@@ -7494,13 +7549,13 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>322</v>
+        <v>247</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>78</v>
@@ -7509,13 +7564,13 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>323</v>
+        <v>248</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>324</v>
+        <v>249</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>325</v>
+        <v>78</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7523,10 +7578,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>326</v>
+        <v>250</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7546,20 +7601,18 @@
         <v>78</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>327</v>
+        <v>103</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>328</v>
+        <v>104</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7608,7 +7661,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>331</v>
+        <v>106</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7620,16 +7673,16 @@
         <v>78</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>333</v>
+        <v>107</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>334</v>
+        <v>78</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -7637,16 +7690,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7662,21 +7713,21 @@
         <v>78</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>209</v>
+        <v>110</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>355</v>
+        <v>111</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>78</v>
       </c>
@@ -7712,19 +7763,19 @@
         <v>78</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>208</v>
+        <v>117</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7736,27 +7787,27 @@
         <v>78</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>216</v>
+        <v>107</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>217</v>
+        <v>78</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>219</v>
+        <v>252</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7776,19 +7827,23 @@
         <v>78</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>104</v>
+        <v>253</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
@@ -7800,7 +7855,7 @@
         <v>78</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>78</v>
+        <v>257</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>78</v>
@@ -7836,7 +7891,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>106</v>
+        <v>258</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7848,13 +7903,13 @@
         <v>78</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>78</v>
+        <v>259</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>107</v>
+        <v>260</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>78</v>
@@ -7865,21 +7920,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>220</v>
+        <v>261</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>78</v>
@@ -7888,19 +7943,19 @@
         <v>78</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>111</v>
+        <v>262</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>112</v>
+        <v>263</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>113</v>
+        <v>264</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7938,37 +7993,37 @@
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>117</v>
+        <v>265</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>107</v>
+        <v>267</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
@@ -7979,10 +8034,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>221</v>
+        <v>268</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7999,7 +8054,7 @@
         <v>78</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>90</v>
@@ -8008,16 +8063,14 @@
         <v>169</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>222</v>
+        <v>269</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>225</v>
+        <v>271</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8042,13 +8095,13 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>227</v>
+        <v>78</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -8066,7 +8119,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>229</v>
+        <v>272</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8081,10 +8134,10 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>192</v>
+        <v>273</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>230</v>
+        <v>274</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -8095,10 +8148,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8106,7 +8159,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>89</v>
@@ -8121,19 +8174,17 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>232</v>
+        <v>103</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8143,7 +8194,7 @@
         <v>78</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>360</v>
+        <v>78</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>78</v>
@@ -8158,13 +8209,13 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>345</v>
+        <v>78</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8182,7 +8233,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>238</v>
+        <v>279</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8197,10 +8248,10 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>239</v>
+        <v>280</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8211,10 +8262,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8222,7 +8273,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>89</v>
@@ -8237,19 +8288,19 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>131</v>
+        <v>283</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>347</v>
+        <v>285</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8259,10 +8310,10 @@
         <v>78</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>362</v>
+        <v>78</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>304</v>
+        <v>78</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>78</v>
@@ -8298,7 +8349,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8313,13 +8364,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>308</v>
+        <v>78</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8327,10 +8378,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8338,7 +8389,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>89</v>
@@ -8356,15 +8407,17 @@
         <v>103</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8376,7 +8429,7 @@
         <v>78</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>313</v>
+        <v>78</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>78</v>
@@ -8412,7 +8465,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8427,13 +8480,13 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>317</v>
+        <v>78</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8441,10 +8494,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8452,7 +8505,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>89</v>
@@ -8467,16 +8520,20 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>319</v>
+        <v>131</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8485,10 +8542,10 @@
         <v>78</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>78</v>
+        <v>356</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>78</v>
+        <v>304</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>78</v>
@@ -8524,7 +8581,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8539,13 +8596,13 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8553,10 +8610,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8564,7 +8621,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>89</v>
@@ -8579,16 +8636,16 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>327</v>
+        <v>103</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8602,7 +8659,7 @@
         <v>78</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>78</v>
+        <v>313</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>78</v>
@@ -8638,7 +8695,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8653,13 +8710,13 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8667,10 +8724,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>366</v>
+        <v>318</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8693,26 +8750,20 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>283</v>
+        <v>319</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>367</v>
+        <v>320</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q59" t="s" s="2">
-        <v>371</v>
-      </c>
+      <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
         <v>78</v>
       </c>
@@ -8756,7 +8807,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>366</v>
+        <v>322</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8771,24 +8822,24 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>78</v>
+        <v>323</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>372</v>
+        <v>324</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>78</v>
+        <v>325</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>373</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>374</v>
+        <v>326</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8799,7 +8850,7 @@
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -8811,20 +8862,18 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>375</v>
+        <v>327</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>376</v>
+        <v>328</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>377</v>
+        <v>329</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
       </c>
@@ -8872,13 +8921,13 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>374</v>
+        <v>331</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>78</v>
@@ -8887,13 +8936,13 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>380</v>
+        <v>332</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>381</v>
+        <v>333</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>382</v>
+        <v>334</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8901,12 +8950,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="D61" t="s" s="2">
         <v>78</v>
       </c>
@@ -8927,19 +8978,17 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>384</v>
+        <v>209</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>388</v>
+        <v>212</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -8988,7 +9037,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>383</v>
+        <v>208</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9003,24 +9052,24 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>389</v>
+        <v>215</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>390</v>
+        <v>216</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>391</v>
+        <v>217</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>392</v>
+        <v>219</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9031,7 +9080,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9040,23 +9089,19 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>393</v>
+        <v>103</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>394</v>
+        <v>104</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9104,28 +9149,28 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>392</v>
+        <v>106</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>398</v>
+        <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>399</v>
+        <v>107</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>400</v>
+        <v>78</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9133,21 +9178,21 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>401</v>
+        <v>365</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>401</v>
+        <v>220</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>78</v>
@@ -9156,21 +9201,21 @@
         <v>78</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>402</v>
+        <v>111</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>78</v>
       </c>
@@ -9194,52 +9239,52 @@
         <v>78</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>405</v>
+        <v>78</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>406</v>
+        <v>78</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>401</v>
+        <v>117</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>407</v>
+        <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>408</v>
+        <v>107</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>409</v>
+        <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9247,10 +9292,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>410</v>
+        <v>366</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>410</v>
+        <v>221</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9267,23 +9312,25 @@
         <v>78</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>411</v>
+        <v>169</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>412</v>
+        <v>222</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="O64" t="s" s="2">
-        <v>414</v>
+        <v>225</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9308,13 +9355,13 @@
         <v>78</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>78</v>
+        <v>227</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>78</v>
+        <v>228</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>78</v>
@@ -9332,7 +9379,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>410</v>
+        <v>229</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9347,13 +9394,13 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>415</v>
+        <v>192</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>416</v>
+        <v>230</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>417</v>
+        <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9361,10 +9408,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>418</v>
+        <v>367</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>418</v>
+        <v>231</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9372,10 +9419,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>78</v>
@@ -9384,20 +9431,22 @@
         <v>78</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>419</v>
+        <v>232</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>420</v>
+        <v>233</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="O65" t="s" s="2">
-        <v>422</v>
+        <v>236</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -9407,7 +9456,7 @@
         <v>78</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>78</v>
+        <v>368</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>78</v>
@@ -9422,13 +9471,11 @@
         <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>78</v>
@@ -9446,13 +9493,13 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>418</v>
+        <v>238</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>78</v>
@@ -9461,13 +9508,13 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>78</v>
+        <v>239</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>423</v>
+        <v>230</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>424</v>
+        <v>78</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
@@ -9475,10 +9522,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>425</v>
+        <v>369</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>425</v>
+        <v>240</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9489,7 +9536,7 @@
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
@@ -9501,13 +9548,13 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>426</v>
+        <v>103</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>427</v>
+        <v>104</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>428</v>
+        <v>105</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9546,38 +9593,40 @@
         <v>78</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AC66" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>425</v>
+        <v>106</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>430</v>
+        <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>431</v>
+        <v>107</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>432</v>
+        <v>78</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>78</v>
@@ -9585,21 +9634,21 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>433</v>
+        <v>370</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>433</v>
+        <v>241</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>78</v>
@@ -9611,15 +9660,17 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -9656,31 +9707,31 @@
         <v>78</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
@@ -9697,14 +9748,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>434</v>
+        <v>371</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>434</v>
+        <v>242</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9720,21 +9771,23 @@
         <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>111</v>
+        <v>243</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>112</v>
+        <v>244</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
       </c>
@@ -9782,7 +9835,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>117</v>
+        <v>247</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9794,13 +9847,13 @@
         <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>107</v>
+        <v>249</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>78</v>
@@ -9811,46 +9864,42 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>435</v>
+        <v>372</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>435</v>
+        <v>250</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>436</v>
+        <v>78</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>437</v>
+        <v>104</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>78</v>
       </c>
@@ -9898,25 +9947,25 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>439</v>
+        <v>106</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -9927,14 +9976,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>440</v>
+        <v>373</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>440</v>
+        <v>251</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9953,18 +10002,18 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>209</v>
+        <v>110</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>441</v>
+        <v>111</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
       </c>
@@ -10000,19 +10049,19 @@
         <v>78</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>440</v>
+        <v>117</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10024,13 +10073,13 @@
         <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>444</v>
+        <v>107</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10041,10 +10090,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>445</v>
+        <v>374</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>445</v>
+        <v>252</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10052,7 +10101,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>89</v>
@@ -10064,19 +10113,23 @@
         <v>78</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>232</v>
+        <v>131</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>446</v>
+        <v>253</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
@@ -10088,7 +10141,7 @@
         <v>78</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>78</v>
+        <v>257</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>78</v>
@@ -10100,13 +10153,13 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -10124,10 +10177,10 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>445</v>
+        <v>258</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>89</v>
@@ -10139,13 +10192,13 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>78</v>
+        <v>259</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>431</v>
+        <v>260</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>450</v>
+        <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -10153,10 +10206,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>451</v>
+        <v>375</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>451</v>
+        <v>261</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10176,21 +10229,21 @@
         <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>319</v>
+        <v>103</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>452</v>
+        <v>262</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10238,7 +10291,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>451</v>
+        <v>265</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10253,13 +10306,13 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>455</v>
+        <v>267</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10267,10 +10320,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>457</v>
+        <v>376</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>457</v>
+        <v>268</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10290,19 +10343,21 @@
         <v>78</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>327</v>
+        <v>169</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>458</v>
+        <v>269</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>459</v>
+        <v>270</v>
       </c>
       <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10350,7 +10405,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>457</v>
+        <v>272</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10365,10 +10420,10 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>460</v>
+        <v>274</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10379,14 +10434,12 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>461</v>
+        <v>377</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C74" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10395,7 +10448,7 @@
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>78</v>
@@ -10404,19 +10457,21 @@
         <v>78</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>426</v>
+        <v>103</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>463</v>
+        <v>276</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>428</v>
+        <v>277</v>
       </c>
       <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10464,13 +10519,13 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>425</v>
+        <v>279</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>78</v>
@@ -10479,13 +10534,13 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>430</v>
+        <v>280</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>431</v>
+        <v>281</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>432</v>
+        <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10493,10 +10548,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>464</v>
+        <v>378</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>433</v>
+        <v>282</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10516,19 +10571,23 @@
         <v>78</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>103</v>
+        <v>283</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>104</v>
+        <v>284</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
       </c>
@@ -10576,7 +10635,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>106</v>
+        <v>288</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10588,13 +10647,13 @@
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>107</v>
+        <v>290</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
@@ -10605,21 +10664,21 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>465</v>
+        <v>379</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>434</v>
+        <v>291</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>78</v>
@@ -10628,21 +10687,23 @@
         <v>78</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>111</v>
+        <v>292</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>112</v>
+        <v>293</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
       </c>
@@ -10690,25 +10751,25 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>117</v>
+        <v>296</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>78</v>
+        <v>297</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>107</v>
+        <v>298</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
@@ -10719,45 +10780,45 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>466</v>
+        <v>380</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>435</v>
+        <v>299</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>436</v>
+        <v>78</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>437</v>
+        <v>300</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>438</v>
+        <v>301</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>113</v>
+        <v>302</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>206</v>
+        <v>303</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -10767,10 +10828,10 @@
         <v>78</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>78</v>
+        <v>381</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>78</v>
+        <v>304</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>78</v>
@@ -10806,28 +10867,28 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>439</v>
+        <v>305</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>78</v>
+        <v>306</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>192</v>
+        <v>307</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>78</v>
+        <v>308</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -10835,10 +10896,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>467</v>
+        <v>382</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>440</v>
+        <v>309</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10846,10 +10907,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -10858,21 +10919,21 @@
         <v>78</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>209</v>
+        <v>103</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>441</v>
+        <v>310</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>78</v>
       </c>
@@ -10884,7 +10945,7 @@
         <v>78</v>
       </c>
       <c r="T78" t="s" s="2">
-        <v>78</v>
+        <v>313</v>
       </c>
       <c r="U78" t="s" s="2">
         <v>78</v>
@@ -10920,13 +10981,13 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>440</v>
+        <v>314</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>78</v>
@@ -10935,13 +10996,13 @@
         <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>78</v>
+        <v>315</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>444</v>
+        <v>316</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>78</v>
+        <v>317</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -10949,10 +11010,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>468</v>
+        <v>383</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>445</v>
+        <v>318</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10960,7 +11021,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>89</v>
@@ -10972,16 +11033,16 @@
         <v>78</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>232</v>
+        <v>319</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>446</v>
+        <v>320</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>447</v>
+        <v>321</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11008,13 +11069,13 @@
         <v>78</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>78</v>
@@ -11032,10 +11093,10 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>445</v>
+        <v>322</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>89</v>
@@ -11047,13 +11108,13 @@
         <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>78</v>
+        <v>323</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>431</v>
+        <v>324</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>450</v>
+        <v>325</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -11061,10 +11122,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>469</v>
+        <v>384</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>470</v>
+        <v>326</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11084,18 +11145,20 @@
         <v>78</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>103</v>
+        <v>327</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>104</v>
+        <v>328</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -11144,7 +11207,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>106</v>
+        <v>331</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11156,16 +11219,16 @@
         <v>78</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>78</v>
+        <v>332</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>107</v>
+        <v>333</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>78</v>
+        <v>334</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11173,21 +11236,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>471</v>
+        <v>385</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>472</v>
+        <v>385</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>78</v>
@@ -11196,25 +11259,29 @@
         <v>78</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>110</v>
+        <v>283</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>111</v>
+        <v>386</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>112</v>
+        <v>387</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q81" s="2"/>
+      <c r="Q81" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="R81" t="s" s="2">
         <v>78</v>
       </c>
@@ -11246,51 +11313,51 @@
         <v>78</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>117</v>
+        <v>385</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>107</v>
+        <v>391</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>473</v>
+        <v>393</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>474</v>
+        <v>393</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11313,19 +11380,19 @@
         <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>147</v>
+        <v>394</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>243</v>
+        <v>395</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>244</v>
+        <v>396</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>245</v>
+        <v>397</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>246</v>
+        <v>398</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -11362,17 +11429,19 @@
         <v>78</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AC82" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>475</v>
+        <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>247</v>
+        <v>393</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11387,13 +11456,13 @@
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>248</v>
+        <v>399</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>249</v>
+        <v>400</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>78</v>
+        <v>401</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -11401,14 +11470,12 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>476</v>
+        <v>402</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11417,7 +11484,7 @@
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>78</v>
@@ -11429,19 +11496,19 @@
         <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>147</v>
+        <v>403</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>243</v>
+        <v>404</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>244</v>
+        <v>405</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>245</v>
+        <v>406</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>246</v>
+        <v>407</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -11466,11 +11533,13 @@
         <v>78</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y83" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z83" t="s" s="2">
-        <v>478</v>
+        <v>78</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
@@ -11488,7 +11557,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>247</v>
+        <v>402</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11503,13 +11572,13 @@
         <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>248</v>
+        <v>408</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>249</v>
+        <v>409</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>78</v>
@@ -11517,14 +11586,12 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>479</v>
+        <v>411</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>78</v>
       </c>
@@ -11533,7 +11600,7 @@
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
@@ -11545,19 +11612,19 @@
         <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>147</v>
+        <v>412</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>243</v>
+        <v>413</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>244</v>
+        <v>414</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>245</v>
+        <v>415</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>246</v>
+        <v>416</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -11582,11 +11649,13 @@
         <v>78</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y84" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z84" t="s" s="2">
-        <v>480</v>
+        <v>78</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>78</v>
@@ -11604,7 +11673,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>247</v>
+        <v>411</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11619,13 +11688,13 @@
         <v>101</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>248</v>
+        <v>417</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>249</v>
+        <v>418</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>78</v>
+        <v>419</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -11633,10 +11702,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>481</v>
+        <v>420</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>482</v>
+        <v>420</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11659,19 +11728,17 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>292</v>
+        <v>421</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>295</v>
+        <v>423</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>78</v>
@@ -11696,13 +11763,13 @@
         <v>78</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>78</v>
+        <v>424</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>78</v>
@@ -11720,7 +11787,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>296</v>
+        <v>420</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11735,13 +11802,13 @@
         <v>101</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>297</v>
+        <v>426</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>298</v>
+        <v>427</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>78</v>
+        <v>428</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
@@ -11749,10 +11816,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>483</v>
+        <v>429</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>451</v>
+        <v>429</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11772,20 +11839,20 @@
         <v>78</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>319</v>
+        <v>430</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>78</v>
@@ -11834,7 +11901,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>451</v>
+        <v>429</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -11849,13 +11916,13 @@
         <v>101</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>78</v>
+        <v>434</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -11863,10 +11930,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>484</v>
+        <v>437</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11877,7 +11944,7 @@
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>78</v>
@@ -11889,16 +11956,18 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>327</v>
+        <v>438</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+      <c r="O87" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
       </c>
@@ -11946,13 +12015,13 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>78</v>
@@ -11964,10 +12033,10 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>78</v>
+        <v>443</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>78</v>
@@ -11975,14 +12044,12 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>485</v>
+        <v>444</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>486</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>78</v>
       </c>
@@ -11991,7 +12058,7 @@
         <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>78</v>
@@ -12003,13 +12070,13 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>487</v>
+        <v>446</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12048,19 +12115,17 @@
         <v>78</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="AC88" s="2"/>
       <c r="AD88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12075,13 +12140,13 @@
         <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>78</v>
@@ -12089,10 +12154,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>488</v>
+        <v>452</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>433</v>
+        <v>452</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12201,10 +12266,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>489</v>
+        <v>453</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12315,14 +12380,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -12344,10 +12409,10 @@
         <v>110</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>437</v>
+        <v>456</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>113</v>
@@ -12402,7 +12467,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12431,10 +12496,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>491</v>
+        <v>459</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12460,14 +12525,14 @@
         <v>209</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -12516,7 +12581,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12534,7 +12599,7 @@
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -12545,10 +12610,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>492</v>
+        <v>464</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12574,10 +12639,10 @@
         <v>232</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12607,10 +12672,10 @@
         <v>159</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>78</v>
@@ -12628,7 +12693,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>89</v>
@@ -12646,10 +12711,10 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -12657,7 +12722,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>470</v>
@@ -12683,16 +12748,18 @@
         <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>104</v>
+        <v>471</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>105</v>
+        <v>472</v>
       </c>
       <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+      <c r="O94" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>78</v>
       </c>
@@ -12740,7 +12807,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>106</v>
+        <v>470</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -12752,16 +12819,16 @@
         <v>78</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>107</v>
+        <v>474</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>78</v>
+        <v>475</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
@@ -12769,21 +12836,21 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>78</v>
@@ -12795,17 +12862,15 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>110</v>
+        <v>327</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>111</v>
+        <v>477</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>78</v>
@@ -12842,37 +12907,37 @@
         <v>78</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>117</v>
+        <v>476</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>107</v>
+        <v>479</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -12883,12 +12948,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C96" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="D96" t="s" s="2">
         <v>78</v>
       </c>
@@ -12906,23 +12973,19 @@
         <v>78</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>147</v>
+        <v>445</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>243</v>
+        <v>482</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>78</v>
       </c>
@@ -12958,17 +13021,19 @@
         <v>78</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AC96" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>475</v>
+        <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>247</v>
+        <v>444</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -12983,13 +13048,13 @@
         <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>248</v>
+        <v>449</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>249</v>
+        <v>450</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>78</v>
+        <v>451</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>78</v>
@@ -12997,14 +13062,12 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>78</v>
       </c>
@@ -13022,23 +13085,19 @@
         <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>498</v>
+        <v>104</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>78</v>
       </c>
@@ -13062,11 +13121,13 @@
         <v>78</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y97" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z97" t="s" s="2">
-        <v>499</v>
+        <v>78</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>78</v>
@@ -13084,25 +13145,25 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>247</v>
+        <v>106</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>249</v>
+        <v>107</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13113,23 +13174,21 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>78</v>
@@ -13138,23 +13197,21 @@
         <v>78</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>502</v>
+        <v>111</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>244</v>
+        <v>112</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>78</v>
       </c>
@@ -13178,11 +13235,13 @@
         <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y98" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z98" t="s" s="2">
-        <v>503</v>
+        <v>78</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>78</v>
@@ -13200,7 +13259,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>247</v>
+        <v>117</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13212,13 +13271,13 @@
         <v>78</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>249</v>
+        <v>107</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
@@ -13229,45 +13288,45 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>504</v>
+        <v>485</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>292</v>
+        <v>456</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>293</v>
+        <v>457</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>294</v>
+        <v>113</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>295</v>
+        <v>206</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13316,25 +13375,25 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>296</v>
+        <v>458</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>297</v>
+        <v>78</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>298</v>
+        <v>192</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>78</v>
@@ -13345,10 +13404,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>505</v>
+        <v>486</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13359,7 +13418,7 @@
         <v>79</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>78</v>
@@ -13371,17 +13430,17 @@
         <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>319</v>
+        <v>209</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -13430,13 +13489,13 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>78</v>
@@ -13448,10 +13507,10 @@
         <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -13459,10 +13518,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13470,7 +13529,7 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>89</v>
@@ -13485,13 +13544,13 @@
         <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13518,13 +13577,13 @@
         <v>78</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>78</v>
+        <v>467</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>78</v>
+        <v>468</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>78</v>
@@ -13542,10 +13601,10 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>89</v>
@@ -13560,10 +13619,10 @@
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>78</v>
+        <v>469</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -13571,14 +13630,12 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>507</v>
+        <v>488</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C102" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>78</v>
       </c>
@@ -13587,7 +13644,7 @@
         <v>79</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>78</v>
@@ -13599,13 +13656,13 @@
         <v>78</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>426</v>
+        <v>103</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>509</v>
+        <v>104</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>428</v>
+        <v>105</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13656,28 +13713,28 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>425</v>
+        <v>106</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>430</v>
+        <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>431</v>
+        <v>107</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>432</v>
+        <v>78</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>78</v>
@@ -13685,21 +13742,21 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>433</v>
+        <v>491</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>78</v>
@@ -13711,15 +13768,17 @@
         <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -13756,31 +13815,31 @@
         <v>78</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>78</v>
@@ -13797,14 +13856,14 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>511</v>
+        <v>492</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>434</v>
+        <v>493</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -13820,21 +13879,23 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>111</v>
+        <v>243</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>112</v>
+        <v>244</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O104" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>78</v>
       </c>
@@ -13870,19 +13931,17 @@
         <v>78</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC104" s="2"/>
       <c r="AD104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>78</v>
+        <v>494</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>117</v>
+        <v>247</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -13894,13 +13953,13 @@
         <v>78</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>107</v>
+        <v>249</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -13911,45 +13970,47 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>512</v>
+        <v>495</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="C105" s="2"/>
+        <v>493</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="D105" t="s" s="2">
-        <v>436</v>
+        <v>78</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>437</v>
+        <v>243</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>438</v>
+        <v>244</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>113</v>
+        <v>245</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>206</v>
+        <v>246</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -13974,13 +14035,11 @@
         <v>78</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y105" s="2"/>
       <c r="Z105" t="s" s="2">
-        <v>78</v>
+        <v>497</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>78</v>
@@ -13998,7 +14057,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>439</v>
+        <v>247</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14010,13 +14069,13 @@
         <v>78</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>192</v>
+        <v>249</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14027,12 +14086,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C106" s="2"/>
+        <v>493</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="D106" t="s" s="2">
         <v>78</v>
       </c>
@@ -14041,7 +14102,7 @@
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>78</v>
@@ -14050,20 +14111,22 @@
         <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>209</v>
+        <v>147</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>441</v>
+        <v>243</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N106" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O106" t="s" s="2">
-        <v>443</v>
+        <v>246</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>78</v>
@@ -14088,13 +14151,11 @@
         <v>78</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y106" s="2"/>
       <c r="Z106" t="s" s="2">
-        <v>78</v>
+        <v>499</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>78</v>
@@ -14112,7 +14173,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>440</v>
+        <v>247</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14127,10 +14188,10 @@
         <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>444</v>
+        <v>249</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
@@ -14141,10 +14202,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>445</v>
+        <v>501</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14152,7 +14213,7 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>89</v>
@@ -14164,19 +14225,23 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>232</v>
+        <v>103</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>446</v>
+        <v>292</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
       </c>
@@ -14200,13 +14265,13 @@
         <v>78</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>78</v>
@@ -14224,10 +14289,10 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>445</v>
+        <v>296</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>89</v>
@@ -14239,13 +14304,13 @@
         <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>78</v>
+        <v>297</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>431</v>
+        <v>298</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>450</v>
+        <v>78</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>78</v>
@@ -14253,7 +14318,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>470</v>
@@ -14279,16 +14344,18 @@
         <v>78</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>104</v>
+        <v>471</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>105</v>
+        <v>472</v>
       </c>
       <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
+      <c r="O108" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>78</v>
       </c>
@@ -14336,7 +14403,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>106</v>
+        <v>470</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14348,16 +14415,16 @@
         <v>78</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>107</v>
+        <v>474</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>78</v>
+        <v>475</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>78</v>
@@ -14365,21 +14432,21 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>78</v>
@@ -14391,17 +14458,15 @@
         <v>78</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>110</v>
+        <v>327</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>111</v>
+        <v>477</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>78</v>
@@ -14438,37 +14503,37 @@
         <v>78</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>117</v>
+        <v>476</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>107</v>
+        <v>479</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -14479,12 +14544,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C110" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="D110" t="s" s="2">
         <v>78</v>
       </c>
@@ -14493,7 +14560,7 @@
         <v>79</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>78</v>
@@ -14502,23 +14569,19 @@
         <v>78</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>147</v>
+        <v>445</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>243</v>
+        <v>506</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>78</v>
       </c>
@@ -14554,17 +14617,19 @@
         <v>78</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AC110" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>475</v>
+        <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>247</v>
+        <v>444</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -14579,13 +14644,13 @@
         <v>101</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>248</v>
+        <v>449</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>249</v>
+        <v>450</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>78</v>
+        <v>451</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>78</v>
@@ -14593,14 +14658,12 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
         <v>78</v>
       </c>
@@ -14618,23 +14681,19 @@
         <v>78</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>520</v>
+        <v>104</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>78</v>
       </c>
@@ -14658,11 +14717,13 @@
         <v>78</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y111" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z111" t="s" s="2">
-        <v>521</v>
+        <v>78</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>78</v>
@@ -14680,25 +14741,25 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>247</v>
+        <v>106</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>249</v>
+        <v>107</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
@@ -14709,23 +14770,21 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>522</v>
+        <v>508</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>78</v>
@@ -14734,23 +14793,21 @@
         <v>78</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>523</v>
+        <v>111</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>244</v>
+        <v>112</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>78</v>
       </c>
@@ -14774,11 +14831,13 @@
         <v>78</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y112" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z112" t="s" s="2">
-        <v>524</v>
+        <v>78</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>78</v>
@@ -14796,7 +14855,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>247</v>
+        <v>117</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -14808,13 +14867,13 @@
         <v>78</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>249</v>
+        <v>107</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -14825,45 +14884,45 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J113" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>292</v>
+        <v>456</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>293</v>
+        <v>457</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>294</v>
+        <v>113</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>295</v>
+        <v>206</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
@@ -14912,25 +14971,25 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>296</v>
+        <v>458</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>297</v>
+        <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>298</v>
+        <v>192</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
@@ -14941,10 +15000,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14955,7 +15014,7 @@
         <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>78</v>
@@ -14967,17 +15026,17 @@
         <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>319</v>
+        <v>209</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>78</v>
@@ -15026,13 +15085,13 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>78</v>
@@ -15044,10 +15103,10 @@
         <v>78</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>78</v>
@@ -15055,10 +15114,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15066,7 +15125,7 @@
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G115" t="s" s="2">
         <v>89</v>
@@ -15081,13 +15140,13 @@
         <v>78</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15114,13 +15173,13 @@
         <v>78</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>78</v>
+        <v>467</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>78</v>
+        <v>468</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>78</v>
@@ -15138,10 +15197,10 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>89</v>
@@ -15156,10 +15215,10 @@
         <v>78</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>78</v>
+        <v>469</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>78</v>
@@ -15167,10 +15226,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>528</v>
+        <v>489</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15181,7 +15240,7 @@
         <v>79</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>78</v>
@@ -15193,20 +15252,16 @@
         <v>78</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>232</v>
+        <v>103</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>529</v>
+        <v>104</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>532</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>78</v>
       </c>
@@ -15230,54 +15285,2568 @@
         <v>78</v>
       </c>
       <c r="X116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="P118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AC118" s="2"/>
+      <c r="AD118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="D119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y119" s="2"/>
+      <c r="Z119" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="D120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="P120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y120" s="2"/>
+      <c r="Z120" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="P121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="P122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N123" s="2"/>
+      <c r="O123" s="2"/>
+      <c r="P123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="D124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
+      <c r="P125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="P127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="P128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
+      <c r="P129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
+      <c r="P130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="P132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AC132" s="2"/>
+      <c r="AD132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C133" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="D133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="P133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y133" s="2"/>
+      <c r="Z133" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="D134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O134" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="P134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y134" s="2"/>
+      <c r="Z134" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="O135" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="P135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N136" s="2"/>
+      <c r="O136" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="P136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
+      <c r="P137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="O138" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="P138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X138" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="Y116" t="s" s="2">
+      <c r="Y138" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Z116" t="s" s="2">
+      <c r="Z138" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AA116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH116" t="s" s="2">
+      <c r="AA138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH138" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AI116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
+      <c r="AI138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK116" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AN116" t="s" s="2">
+      <c r="AK138" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AN138" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -679,11 +679,11 @@
     <t>Often, specific identities are assigned for the agent.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:system}
+    <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
-    <t>Slice based on the identifier.system pattern</t>
+    <t>Slice based on the identifier.system value</t>
   </si>
   <si>
     <t>PRD-7 (or XCN.1)</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3824" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4183" uniqueCount="557">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1028,6 +1028,213 @@
   </si>
   <si>
     <t>./PreferredName (GivenNames, FamilyName, TitleCode)</t>
+  </si>
+  <si>
+    <t>Practitioner.name.id</t>
+  </si>
+  <si>
+    <t>Practitioner.name.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.name.extension:assemblyOrder</t>
+  </si>
+  <si>
+    <t>assemblyOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {humanname-assembly-order|5.2.0}
+</t>
+  </si>
+  <si>
+    <t>Preferred display order of name parts</t>
+  </si>
+  <si>
+    <t>A code that represents the preferred display order of the components of this human name.</t>
+  </si>
+  <si>
+    <t>Practitioner.name.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this name.</t>
+  </si>
+  <si>
+    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>The use of a human name.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
+  </si>
+  <si>
+    <t>HumanName.use</t>
+  </si>
+  <si>
+    <t>XPN.7, but often indicated by which field contains the name</t>
+  </si>
+  <si>
+    <t>unique(./use)</t>
+  </si>
+  <si>
+    <t>./NamePurpose</t>
+  </si>
+  <si>
+    <t>Practitioner.name.text</t>
+  </si>
+  <si>
+    <t>Text representation of the full name</t>
+  </si>
+  <si>
+    <t>Specifies the entire name as it should be displayed e.g. on an application UI. This may be provided instead of or as well as the specific parts.</t>
+  </si>
+  <si>
+    <t>Can provide both a text representation and parts. Applications updating a name SHALL ensure that when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
+  </si>
+  <si>
+    <t>A renderable, unencoded form.</t>
+  </si>
+  <si>
+    <t>HumanName.text</t>
+  </si>
+  <si>
+    <t>implied by XPN.11</t>
+  </si>
+  <si>
+    <t>./formatted</t>
+  </si>
+  <si>
+    <t>Practitioner.name.family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">surname
+</t>
+  </si>
+  <si>
+    <t>Family name (often called 'Surname')</t>
+  </si>
+  <si>
+    <t>The part of a name that links to the genealogy. In some cultures (e.g. Eritrea) the family name of a son is the first name of his father.</t>
+  </si>
+  <si>
+    <t>Family Name may be decomposed into specific parts using extensions (de, nl, es related cultures).</t>
+  </si>
+  <si>
+    <t>HumanName.family</t>
+  </si>
+  <si>
+    <t>XPN.1/FN.1</t>
+  </si>
+  <si>
+    <t>./part[partType = FAM]</t>
+  </si>
+  <si>
+    <t>./FamilyName</t>
+  </si>
+  <si>
+    <t>Practitioner.name.given</t>
+  </si>
+  <si>
+    <t>first name
+middle name</t>
+  </si>
+  <si>
+    <t>Given names (not always 'first'). Includes middle names</t>
+  </si>
+  <si>
+    <t>Given name.</t>
+  </si>
+  <si>
+    <t>If only initials are recorded, they may be used in place of the full name parts. Initials may be separated into multiple given names but often aren't due to paractical limitations.  This element is not called "first name" since given names do not always come first.</t>
+  </si>
+  <si>
+    <t>HumanName.given</t>
+  </si>
+  <si>
+    <t>XPN.2 + XPN.3</t>
+  </si>
+  <si>
+    <t>./part[partType = GIV]</t>
+  </si>
+  <si>
+    <t>./GivenNames</t>
+  </si>
+  <si>
+    <t>Practitioner.name.prefix</t>
+  </si>
+  <si>
+    <t>Parts that come before the name</t>
+  </si>
+  <si>
+    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
+  </si>
+  <si>
+    <t>Civilités des personnes physiques</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J78-Civilite-RASS/FHIR/JDV-J78-Civilite-RASS</t>
+  </si>
+  <si>
+    <t>HumanName.prefix</t>
+  </si>
+  <si>
+    <t>XPN.5</t>
+  </si>
+  <si>
+    <t>./part[partType = PFX]</t>
+  </si>
+  <si>
+    <t>./TitleCode</t>
+  </si>
+  <si>
+    <t>Practitioner.name.suffix</t>
+  </si>
+  <si>
+    <t>jeu de valeurs pour spécifier le titre de la personne</t>
+  </si>
+  <si>
+    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
+  </si>
+  <si>
+    <t>Civilités d'exercice d'un professionnel du RASS</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J79-CiviliteExercice-RASS/FHIR/JDV-J79-CiviliteExercice-RASS</t>
+  </si>
+  <si>
+    <t>HumanName.suffix</t>
+  </si>
+  <si>
+    <t>XPN/4</t>
+  </si>
+  <si>
+    <t>./part[partType = SFX]</t>
+  </si>
+  <si>
+    <t>Practitioner.name.period</t>
+  </si>
+  <si>
+    <t>Time period when name was/is in use</t>
+  </si>
+  <si>
+    <t>Indicates the period of time when this name was valid for the named person.</t>
+  </si>
+  <si>
+    <t>Allows names to be placed in historical context.</t>
+  </si>
+  <si>
+    <t>HumanName.period</t>
+  </si>
+  <si>
+    <t>XPN.13 + XPN.14</t>
+  </si>
+  <si>
+    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
   </si>
   <si>
     <t>Practitioner.telecom</t>
@@ -1848,7 +2055,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN105"/>
+  <dimension ref="A1:AN115"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.98046875" customWidth="true" bestFit="true"/>
@@ -1886,7 +2093,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="39.109375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="48.16015625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="44.90625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
@@ -7506,7 +7713,7 @@
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>78</v>
@@ -7515,23 +7722,19 @@
         <v>78</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>323</v>
+        <v>103</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>324</v>
+        <v>104</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>78</v>
       </c>
@@ -7579,28 +7782,28 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>322</v>
+        <v>106</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>328</v>
+        <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>329</v>
+        <v>107</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>330</v>
+        <v>78</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7608,14 +7811,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7631,23 +7834,21 @@
         <v>78</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>332</v>
+        <v>110</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>333</v>
+        <v>111</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>334</v>
+        <v>112</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
@@ -7683,19 +7884,19 @@
         <v>78</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>331</v>
+        <v>117</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7707,16 +7908,16 @@
         <v>78</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>337</v>
+        <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>338</v>
+        <v>107</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>339</v>
+        <v>78</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -7724,12 +7925,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="D52" t="s" s="2">
         <v>78</v>
       </c>
@@ -7747,21 +7950,19 @@
         <v>78</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>169</v>
+        <v>326</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>343</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>78</v>
       </c>
@@ -7785,13 +7986,13 @@
         <v>78</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>345</v>
+        <v>78</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
@@ -7809,28 +8010,28 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>340</v>
+        <v>117</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>346</v>
+        <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>347</v>
+        <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>348</v>
+        <v>78</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -7838,10 +8039,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7858,23 +8059,25 @@
         <v>78</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>350</v>
+        <v>169</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -7899,13 +8102,13 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>78</v>
+        <v>334</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>78</v>
+        <v>335</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -7923,7 +8126,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7938,13 +8141,13 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -7952,10 +8155,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7966,7 +8169,7 @@
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>78</v>
@@ -7975,20 +8178,22 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>358</v>
+        <v>103</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8037,13 +8242,13 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>78</v>
@@ -8052,13 +8257,13 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>78</v>
+        <v>346</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>363</v>
+        <v>78</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8066,21 +8271,21 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>78</v>
+        <v>349</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>78</v>
@@ -8089,18 +8294,20 @@
         <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>365</v>
+        <v>103</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8137,23 +8344,25 @@
         <v>78</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AC55" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>78</v>
@@ -8162,13 +8371,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8176,21 +8385,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>78</v>
+        <v>358</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
@@ -8199,18 +8408,20 @@
         <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>104</v>
+        <v>359</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8259,28 +8470,28 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>106</v>
+        <v>362</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>78</v>
+        <v>363</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>107</v>
+        <v>364</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>78</v>
+        <v>365</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8288,21 +8499,21 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>78</v>
@@ -8311,20 +8522,18 @@
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>111</v>
+        <v>367</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8349,13 +8558,13 @@
         <v>78</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>78</v>
+        <v>369</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>78</v>
+        <v>370</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -8373,7 +8582,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>117</v>
+        <v>371</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8385,16 +8594,16 @@
         <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>78</v>
+        <v>372</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>107</v>
+        <v>373</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>78</v>
+        <v>374</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8402,14 +8611,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>375</v>
+        <v>78</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8422,13 +8631,13 @@
         <v>78</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>376</v>
@@ -8436,12 +8645,8 @@
       <c r="M58" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="N58" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>206</v>
-      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>78</v>
       </c>
@@ -8465,13 +8670,13 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>78</v>
+        <v>378</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>78</v>
+        <v>379</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -8489,7 +8694,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8501,13 +8706,13 @@
         <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>78</v>
+        <v>381</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>192</v>
+        <v>382</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8518,10 +8723,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8532,7 +8737,7 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
@@ -8541,20 +8746,20 @@
         <v>78</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>209</v>
+        <v>260</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8603,13 +8808,13 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>78</v>
@@ -8618,13 +8823,13 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>78</v>
+        <v>388</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -8632,10 +8837,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8643,10 +8848,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -8655,19 +8860,23 @@
         <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>232</v>
+        <v>391</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
       </c>
@@ -8691,13 +8900,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>387</v>
+        <v>78</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>388</v>
+        <v>78</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -8715,13 +8924,13 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>78</v>
@@ -8730,13 +8939,13 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>78</v>
+        <v>396</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8744,10 +8953,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8758,7 +8967,7 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>78</v>
@@ -8767,20 +8976,22 @@
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>260</v>
+        <v>400</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="O61" t="s" s="2">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -8829,13 +9040,13 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>78</v>
@@ -8844,13 +9055,13 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>78</v>
+        <v>405</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -8858,10 +9069,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8881,19 +9092,21 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>268</v>
+        <v>169</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
@@ -8917,13 +9130,13 @@
         <v>78</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>78</v>
+        <v>412</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
@@ -8941,7 +9154,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8956,13 +9169,13 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>78</v>
+        <v>416</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -8970,14 +9183,12 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>78</v>
       </c>
@@ -8986,7 +9197,7 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>78</v>
@@ -8995,19 +9206,21 @@
         <v>78</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>365</v>
+        <v>418</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>367</v>
+        <v>420</v>
       </c>
       <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
       </c>
@@ -9055,13 +9268,13 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>364</v>
+        <v>417</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>78</v>
@@ -9070,13 +9283,13 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>369</v>
+        <v>422</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>370</v>
+        <v>423</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>371</v>
+        <v>424</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9084,10 +9297,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>372</v>
+        <v>425</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9098,7 +9311,7 @@
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>78</v>
@@ -9110,16 +9323,18 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>103</v>
+        <v>426</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>104</v>
+        <v>427</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>105</v>
+        <v>428</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9167,28 +9382,28 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>106</v>
+        <v>425</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>107</v>
+        <v>430</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>78</v>
+        <v>431</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9196,14 +9411,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>404</v>
+        <v>432</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9222,17 +9437,15 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>110</v>
+        <v>433</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>111</v>
+        <v>434</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -9269,19 +9482,17 @@
         <v>78</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="AC65" s="2"/>
       <c r="AD65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>117</v>
+        <v>432</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9293,16 +9504,16 @@
         <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>78</v>
+        <v>437</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>107</v>
+        <v>438</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
@@ -9310,46 +9521,42 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>405</v>
+        <v>440</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>374</v>
+        <v>440</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>375</v>
+        <v>78</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>376</v>
+        <v>104</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9397,25 +9604,25 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>378</v>
+        <v>106</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9426,14 +9633,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>406</v>
+        <v>441</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>379</v>
+        <v>441</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9452,18 +9659,18 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>209</v>
+        <v>110</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>380</v>
+        <v>111</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>78</v>
       </c>
@@ -9511,7 +9718,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>379</v>
+        <v>117</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9523,13 +9730,13 @@
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>383</v>
+        <v>107</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -9540,42 +9747,46 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>407</v>
+        <v>442</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>384</v>
+        <v>442</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>78</v>
+        <v>443</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>232</v>
+        <v>110</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>385</v>
+        <v>444</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
       </c>
@@ -9599,13 +9810,13 @@
         <v>78</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>387</v>
+        <v>78</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>388</v>
+        <v>78</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -9623,28 +9834,28 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>384</v>
+        <v>446</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>370</v>
+        <v>192</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>78</v>
@@ -9652,10 +9863,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>409</v>
+        <v>447</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9666,7 +9877,7 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
@@ -9678,16 +9889,18 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>103</v>
+        <v>209</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>104</v>
+        <v>448</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>105</v>
+        <v>449</v>
       </c>
       <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
       </c>
@@ -9735,25 +9948,25 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>106</v>
+        <v>447</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>107</v>
+        <v>451</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -9764,21 +9977,21 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>410</v>
+        <v>452</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>411</v>
+        <v>452</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>78</v>
@@ -9790,17 +10003,15 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>110</v>
+        <v>232</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>111</v>
+        <v>453</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -9825,52 +10036,52 @@
         <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>78</v>
+        <v>456</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>117</v>
+        <v>452</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>107</v>
+        <v>438</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
@@ -9878,10 +10089,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>412</v>
+        <v>458</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9892,7 +10103,7 @@
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>78</v>
@@ -9901,22 +10112,20 @@
         <v>78</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>147</v>
+        <v>260</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>414</v>
+        <v>459</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>417</v>
+        <v>461</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -9953,23 +10162,25 @@
         <v>78</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AC71" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>418</v>
+        <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>419</v>
+        <v>458</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>78</v>
@@ -9978,13 +10189,13 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>421</v>
+        <v>462</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>78</v>
+        <v>463</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -9992,14 +10203,12 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>422</v>
+        <v>464</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="C72" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10017,23 +10226,19 @@
         <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>147</v>
+        <v>268</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>414</v>
+        <v>465</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10057,11 +10262,13 @@
         <v>78</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>424</v>
+        <v>78</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -10079,13 +10286,13 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>419</v>
+        <v>464</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>78</v>
@@ -10094,10 +10301,10 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>421</v>
+        <v>467</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10108,13 +10315,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>425</v>
+        <v>468</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>401</v>
+        <v>469</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>78</v>
@@ -10124,7 +10331,7 @@
         <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>78</v>
@@ -10133,23 +10340,19 @@
         <v>78</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>147</v>
+        <v>433</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10173,11 +10376,13 @@
         <v>78</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>426</v>
+        <v>78</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>78</v>
@@ -10195,7 +10400,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10210,13 +10415,13 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10224,10 +10429,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>427</v>
+        <v>471</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10247,23 +10452,19 @@
         <v>78</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>429</v>
+        <v>104</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10311,7 +10512,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>433</v>
+        <v>106</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10323,13 +10524,13 @@
         <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>434</v>
+        <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>435</v>
+        <v>107</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10340,21 +10541,21 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>436</v>
+        <v>472</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>390</v>
+        <v>441</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
@@ -10366,18 +10567,18 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>391</v>
+        <v>111</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>78</v>
       </c>
@@ -10425,28 +10626,28 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>390</v>
+        <v>117</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>394</v>
+        <v>107</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>395</v>
+        <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -10454,42 +10655,46 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>396</v>
+        <v>442</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>78</v>
+        <v>443</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>268</v>
+        <v>110</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>397</v>
+        <v>444</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
       </c>
@@ -10537,25 +10742,25 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>396</v>
+        <v>446</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>399</v>
+        <v>192</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
@@ -10566,14 +10771,12 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>438</v>
+        <v>474</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>78</v>
       </c>
@@ -10582,7 +10785,7 @@
         <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>78</v>
@@ -10594,16 +10797,18 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>365</v>
+        <v>209</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>367</v>
+        <v>449</v>
       </c>
       <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>78</v>
       </c>
@@ -10651,7 +10856,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>364</v>
+        <v>447</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10666,13 +10871,13 @@
         <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>369</v>
+        <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>370</v>
+        <v>451</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>371</v>
+        <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -10680,10 +10885,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>441</v>
+        <v>475</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>372</v>
+        <v>452</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10691,7 +10896,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>89</v>
@@ -10706,13 +10911,13 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>103</v>
+        <v>232</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>104</v>
+        <v>453</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>105</v>
+        <v>454</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10739,13 +10944,13 @@
         <v>78</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>78</v>
+        <v>456</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>78</v>
@@ -10763,10 +10968,10 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>106</v>
+        <v>452</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>89</v>
@@ -10775,16 +10980,16 @@
         <v>78</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>107</v>
+        <v>438</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -10792,21 +10997,21 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>442</v>
+        <v>476</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>373</v>
+        <v>477</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>78</v>
@@ -10818,17 +11023,15 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -10877,19 +11080,19 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
@@ -10906,14 +11109,14 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>443</v>
+        <v>478</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>374</v>
+        <v>479</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>375</v>
+        <v>109</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -10926,26 +11129,24 @@
         <v>78</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>376</v>
+        <v>111</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>377</v>
+        <v>112</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O80" t="s" s="2">
-        <v>206</v>
-      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
       </c>
@@ -10981,19 +11182,19 @@
         <v>78</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>378</v>
+        <v>117</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11011,7 +11212,7 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>78</v>
@@ -11022,10 +11223,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>444</v>
+        <v>480</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>379</v>
+        <v>481</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11045,20 +11246,22 @@
         <v>78</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>209</v>
+        <v>147</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>380</v>
+        <v>482</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="O81" t="s" s="2">
-        <v>382</v>
+        <v>485</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
@@ -11095,19 +11298,17 @@
         <v>78</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC81" s="2"/>
       <c r="AD81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>78</v>
+        <v>486</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>379</v>
+        <v>487</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11122,10 +11323,10 @@
         <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>78</v>
+        <v>488</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>383</v>
+        <v>489</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
@@ -11136,18 +11337,20 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>445</v>
+        <v>490</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="C82" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="D82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>89</v>
@@ -11159,19 +11362,23 @@
         <v>78</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>232</v>
+        <v>147</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>385</v>
+        <v>482</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
       </c>
@@ -11195,13 +11402,11 @@
         <v>78</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>388</v>
+        <v>492</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -11219,13 +11424,13 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>384</v>
+        <v>487</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>78</v>
@@ -11234,13 +11439,13 @@
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>78</v>
+        <v>488</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>370</v>
+        <v>489</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -11248,12 +11453,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>446</v>
+        <v>493</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C83" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="D83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11271,19 +11478,23 @@
         <v>78</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>104</v>
+        <v>482</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11307,13 +11518,11 @@
         <v>78</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>78</v>
+        <v>494</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
@@ -11331,25 +11540,25 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>106</v>
+        <v>487</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>78</v>
+        <v>488</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>107</v>
+        <v>489</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11360,21 +11569,21 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>447</v>
+        <v>495</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>411</v>
+        <v>496</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
@@ -11383,21 +11592,23 @@
         <v>78</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>111</v>
+        <v>497</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>112</v>
+        <v>498</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
       </c>
@@ -11433,37 +11644,37 @@
         <v>78</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>117</v>
+        <v>501</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>78</v>
+        <v>502</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>107</v>
+        <v>503</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
@@ -11474,10 +11685,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>448</v>
+        <v>504</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11488,7 +11699,7 @@
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>78</v>
@@ -11497,22 +11708,20 @@
         <v>78</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>147</v>
+        <v>260</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>414</v>
+        <v>459</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>417</v>
+        <v>461</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>78</v>
@@ -11549,23 +11758,25 @@
         <v>78</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AC85" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>418</v>
+        <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>419</v>
+        <v>458</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>78</v>
@@ -11574,13 +11785,13 @@
         <v>101</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>421</v>
+        <v>462</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>78</v>
+        <v>463</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
@@ -11588,14 +11799,12 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>449</v>
+        <v>505</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>78</v>
       </c>
@@ -11613,23 +11822,19 @@
         <v>78</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>147</v>
+        <v>268</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>78</v>
       </c>
@@ -11653,11 +11858,13 @@
         <v>78</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y86" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z86" t="s" s="2">
-        <v>452</v>
+        <v>78</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>78</v>
@@ -11675,13 +11882,13 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>419</v>
+        <v>464</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>78</v>
@@ -11690,10 +11897,10 @@
         <v>101</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>421</v>
+        <v>467</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>78</v>
@@ -11704,13 +11911,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>453</v>
+        <v>506</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>454</v>
+        <v>507</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>78</v>
@@ -11729,23 +11936,19 @@
         <v>78</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>147</v>
+        <v>433</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>78</v>
       </c>
@@ -11769,11 +11972,13 @@
         <v>78</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y87" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z87" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>78</v>
@@ -11791,7 +11996,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -11806,13 +12011,13 @@
         <v>101</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>78</v>
@@ -11820,10 +12025,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>457</v>
+        <v>509</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11843,23 +12048,19 @@
         <v>78</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>429</v>
+        <v>104</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>78</v>
       </c>
@@ -11907,7 +12108,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>433</v>
+        <v>106</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -11919,13 +12120,13 @@
         <v>78</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>434</v>
+        <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>435</v>
+        <v>107</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -11936,21 +12137,21 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>458</v>
+        <v>510</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>390</v>
+        <v>441</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>78</v>
@@ -11962,18 +12163,18 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>391</v>
+        <v>111</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>78</v>
       </c>
@@ -12021,28 +12222,28 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>390</v>
+        <v>117</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>394</v>
+        <v>107</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>395</v>
+        <v>78</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>78</v>
@@ -12050,42 +12251,46 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>459</v>
+        <v>511</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>396</v>
+        <v>442</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>78</v>
+        <v>443</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>268</v>
+        <v>110</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>397</v>
+        <v>444</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
       </c>
@@ -12133,25 +12338,25 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>396</v>
+        <v>446</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>399</v>
+        <v>192</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12162,14 +12367,12 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>460</v>
+        <v>512</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C91" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>78</v>
       </c>
@@ -12190,16 +12393,18 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>365</v>
+        <v>209</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>367</v>
+        <v>449</v>
       </c>
       <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
       </c>
@@ -12247,7 +12452,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>364</v>
+        <v>447</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12262,13 +12467,13 @@
         <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>369</v>
+        <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>370</v>
+        <v>451</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>371</v>
+        <v>78</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>78</v>
@@ -12276,10 +12481,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>463</v>
+        <v>513</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>372</v>
+        <v>452</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12287,7 +12492,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>89</v>
@@ -12302,13 +12507,13 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>103</v>
+        <v>232</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>104</v>
+        <v>453</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>105</v>
+        <v>454</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12335,13 +12540,13 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>78</v>
+        <v>456</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -12359,10 +12564,10 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>106</v>
+        <v>452</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>89</v>
@@ -12371,16 +12576,16 @@
         <v>78</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>107</v>
+        <v>438</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -12388,21 +12593,21 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>464</v>
+        <v>514</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>373</v>
+        <v>477</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>78</v>
@@ -12414,17 +12619,15 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -12473,19 +12676,19 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>78</v>
@@ -12502,14 +12705,14 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>465</v>
+        <v>515</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>374</v>
+        <v>479</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>375</v>
+        <v>109</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -12522,26 +12725,24 @@
         <v>78</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>376</v>
+        <v>111</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>377</v>
+        <v>112</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O94" t="s" s="2">
-        <v>206</v>
-      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>78</v>
       </c>
@@ -12577,19 +12778,19 @@
         <v>78</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>378</v>
+        <v>117</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -12607,7 +12808,7 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
@@ -12618,10 +12819,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>466</v>
+        <v>516</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>379</v>
+        <v>481</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12641,20 +12842,22 @@
         <v>78</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>209</v>
+        <v>147</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>380</v>
+        <v>482</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="O95" t="s" s="2">
-        <v>382</v>
+        <v>485</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>78</v>
@@ -12691,19 +12894,17 @@
         <v>78</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC95" s="2"/>
       <c r="AD95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>78</v>
+        <v>486</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>379</v>
+        <v>487</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -12718,10 +12919,10 @@
         <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>78</v>
+        <v>488</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>383</v>
+        <v>489</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -12732,18 +12933,20 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>467</v>
+        <v>517</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="C96" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="D96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>89</v>
@@ -12755,19 +12958,23 @@
         <v>78</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>232</v>
+        <v>147</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>385</v>
+        <v>519</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>78</v>
       </c>
@@ -12791,13 +12998,11 @@
         <v>78</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y96" s="2"/>
       <c r="Z96" t="s" s="2">
-        <v>388</v>
+        <v>520</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>78</v>
@@ -12815,13 +13020,13 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>384</v>
+        <v>487</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>78</v>
@@ -12830,13 +13035,13 @@
         <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>78</v>
+        <v>488</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>370</v>
+        <v>489</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>78</v>
@@ -12844,12 +13049,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>468</v>
+        <v>521</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C97" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="D97" t="s" s="2">
         <v>78</v>
       </c>
@@ -12867,19 +13074,23 @@
         <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>104</v>
+        <v>523</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
       </c>
@@ -12903,13 +13114,11 @@
         <v>78</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>78</v>
+        <v>524</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>78</v>
@@ -12927,25 +13136,25 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>106</v>
+        <v>487</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>78</v>
+        <v>488</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>107</v>
+        <v>489</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -12956,21 +13165,21 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>469</v>
+        <v>525</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>411</v>
+        <v>496</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>78</v>
@@ -12979,21 +13188,23 @@
         <v>78</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>111</v>
+        <v>497</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>112</v>
+        <v>498</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O98" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>78</v>
       </c>
@@ -13029,37 +13240,37 @@
         <v>78</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>117</v>
+        <v>501</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>78</v>
+        <v>502</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>107</v>
+        <v>503</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
@@ -13070,10 +13281,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>470</v>
+        <v>526</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13084,7 +13295,7 @@
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>78</v>
@@ -13093,22 +13304,20 @@
         <v>78</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>147</v>
+        <v>260</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>414</v>
+        <v>459</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>417</v>
+        <v>461</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13145,23 +13354,25 @@
         <v>78</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AC99" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>418</v>
+        <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>419</v>
+        <v>458</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>78</v>
@@ -13170,13 +13381,13 @@
         <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>421</v>
+        <v>462</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>78</v>
+        <v>463</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
@@ -13184,14 +13395,12 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>471</v>
+        <v>527</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="C100" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>78</v>
       </c>
@@ -13209,23 +13418,19 @@
         <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>147</v>
+        <v>268</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>78</v>
       </c>
@@ -13249,11 +13454,13 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y100" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z100" t="s" s="2">
-        <v>474</v>
+        <v>78</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>78</v>
@@ -13271,13 +13478,13 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>419</v>
+        <v>464</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>78</v>
@@ -13286,10 +13493,10 @@
         <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>421</v>
+        <v>467</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>78</v>
@@ -13300,13 +13507,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>475</v>
+        <v>528</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>461</v>
+        <v>529</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>78</v>
@@ -13316,7 +13523,7 @@
         <v>79</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
@@ -13325,23 +13532,19 @@
         <v>78</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>147</v>
+        <v>433</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>476</v>
+        <v>530</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>78</v>
       </c>
@@ -13365,11 +13568,13 @@
         <v>78</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y101" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z101" t="s" s="2">
-        <v>477</v>
+        <v>78</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>78</v>
@@ -13387,7 +13592,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13402,13 +13607,13 @@
         <v>101</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -13416,10 +13621,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>478</v>
+        <v>531</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13439,23 +13644,19 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K102" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>429</v>
+        <v>104</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>78</v>
       </c>
@@ -13503,7 +13704,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>433</v>
+        <v>106</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -13515,13 +13716,13 @@
         <v>78</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>434</v>
+        <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>435</v>
+        <v>107</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
@@ -13532,21 +13733,21 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>479</v>
+        <v>532</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>390</v>
+        <v>441</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>78</v>
@@ -13558,18 +13759,18 @@
         <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>391</v>
+        <v>111</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>78</v>
       </c>
@@ -13617,28 +13818,28 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>390</v>
+        <v>117</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>394</v>
+        <v>107</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>395</v>
+        <v>78</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>78</v>
@@ -13646,42 +13847,46 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>480</v>
+        <v>533</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>396</v>
+        <v>442</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>78</v>
+        <v>443</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>268</v>
+        <v>110</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>397</v>
+        <v>444</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>78</v>
       </c>
@@ -13729,25 +13934,25 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>396</v>
+        <v>446</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>399</v>
+        <v>192</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -13758,10 +13963,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>481</v>
+        <v>534</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>481</v>
+        <v>447</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13784,19 +13989,17 @@
         <v>78</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>482</v>
+        <v>448</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>485</v>
+        <v>450</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -13821,13 +14024,13 @@
         <v>78</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>78</v>
@@ -13845,7 +14048,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>481</v>
+        <v>447</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -13860,15 +14063,1157 @@
         <v>101</v>
       </c>
       <c r="AK105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AC109" s="2"/>
+      <c r="AD109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE109" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="AL105" t="s" s="2">
+      <c r="AF109" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AM105" t="s" s="2">
+      <c r="AG109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK109" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AN105" t="s" s="2">
+      <c r="AL109" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="D110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y110" s="2"/>
+      <c r="Z110" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="D111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y111" s="2"/>
+      <c r="Z111" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="P112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="P113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="P115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AN115" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1042,7 +1042,7 @@
     <t>assemblyOrder</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {humanname-assembly-order|5.2.0}
+    <t xml:space="preserve">Extension {humanname-assembly-order|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -1177,7 +1177,7 @@
     <t>Civilités des personnes physiques</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J78-Civilite-RASS/FHIR/JDV-J78-Civilite-RASS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J245-Civilite-CISIS/FHIR/JDV-J245-Civilite-CISIS</t>
   </si>
   <si>
     <t>HumanName.prefix</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Practitioner|4.0.1</t>
+    <t>http://hl7.eu/fhir/base/StructureDefinition/practitioner-eu-core|2.0.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}name-or-identifier:identifier or name SHALL be present {identifier.exists() or name.exists()}</t>
   </si>
   <si>
     <t>PRD (as one example)</t>
@@ -673,7 +673,7 @@
 </t>
   </si>
   <si>
-    <t>An identifier for the person as this agent</t>
+    <t>Practitioner identifier</t>
   </si>
   <si>
     <t>An identifier that applies to this person in this role.</t>
@@ -1004,7 +1004,7 @@
 </t>
   </si>
   <si>
-    <t>The name(s) associated with the practitioner</t>
+    <t>Practitioner Name</t>
   </si>
   <si>
     <t>The name(s) associated with the practitioner.</t>
@@ -1247,7 +1247,7 @@
 </t>
   </si>
   <si>
-    <t>A contact detail for the practitioner (that apply to all roles)</t>
+    <t>Contact details for the practitioner</t>
   </si>
   <si>
     <t>A contact detail for the practitioner, e.g. a telephone number or an email address.</t>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
